--- a/auto-print/format_for_turf_tracker.xlsx
+++ b/auto-print/format_for_turf_tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/glow/Documents/personal/hong/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/glow/sourcecode/github-personal/ngp-van-data-entry-doc/auto-print/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D54C4826-2E35-DD49-BE4A-363FCC02A8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC14234-B8A2-D94E-AC60-46A53E24DEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17160" xr2:uid="{DA986697-404D-AD4E-9614-1C1B5DD93203}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Misname" sheetId="4" r:id="rId3"/>
     <sheet name="Sort" sheetId="7" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="311">
   <si>
     <t>civil_district_name</t>
   </si>
@@ -963,6 +963,18 @@
   </si>
   <si>
     <t>duplicate_finder</t>
+  </si>
+  <si>
+    <t>Paste CSV here</t>
+  </si>
+  <si>
+    <t>Use Misname tab</t>
+  </si>
+  <si>
+    <t>Final output here (copy/paste to Sort for sorting)</t>
+  </si>
+  <si>
+    <t>Find duplicates</t>
   </si>
 </sst>
 </file>
@@ -1129,12 +1141,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1144,6 +1156,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1205,18 +1220,9 @@
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF7F7F7F"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1301,9 +1307,15 @@
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF7F7F7F"/>
+        </top>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1319,8 +1331,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FE932A76-FA88-BD42-8519-BBE3738C6979}" name="Table5" displayName="Table5" ref="A1:G138" totalsRowShown="0" tableBorderDxfId="5">
-  <autoFilter ref="A1:G138" xr:uid="{FE932A76-FA88-BD42-8519-BBE3738C6979}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FE932A76-FA88-BD42-8519-BBE3738C6979}" name="Table5" displayName="Table5" ref="A2:G139" totalsRowShown="0" tableBorderDxfId="9">
+  <autoFilter ref="A2:G139" xr:uid="{FE932A76-FA88-BD42-8519-BBE3738C6979}"/>
   <tableColumns count="7">
     <tableColumn id="7" xr3:uid="{3E2B1255-B64E-BF44-960A-B1CE96520ECE}" name="region_name_raw"/>
     <tableColumn id="1" xr3:uid="{27C60891-9647-A248-8FD4-1CA4B7E97745}" name="civil_district_name"/>
@@ -1335,11 +1347,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{10975CCF-9792-BD44-9119-0D9E121161F1}" name="Table6" displayName="Table6" ref="H1:H138" totalsRowShown="0" headerRowCellStyle="Normal">
-  <autoFilter ref="H1:H138" xr:uid="{10975CCF-9792-BD44-9119-0D9E121161F1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{10975CCF-9792-BD44-9119-0D9E121161F1}" name="Table6" displayName="Table6" ref="H2:H139" totalsRowShown="0" headerRowCellStyle="Normal">
+  <autoFilter ref="H2:H139" xr:uid="{10975CCF-9792-BD44-9119-0D9E121161F1}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{1DBC5718-9024-8C45-B9C1-5D5A20189353}" name="misname_rename">
-      <calculatedColumnFormula>_xlfn.XLOOKUP($B2,Table24[Misname],Table24[Canonical],$B2)</calculatedColumnFormula>
+      <calculatedColumnFormula>_xlfn.XLOOKUP($B3,Table24[Misname],Table24[Canonical],$B3)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1347,23 +1359,23 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C46EEB7E-A7CB-C246-8ADB-5D6D5EF2C1F5}" name="Table7" displayName="Table7" ref="I1:M138" totalsRowShown="0" headerRowCellStyle="Normal">
-  <autoFilter ref="I1:M138" xr:uid="{C46EEB7E-A7CB-C246-8ADB-5D6D5EF2C1F5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C46EEB7E-A7CB-C246-8ADB-5D6D5EF2C1F5}" name="Table7" displayName="Table7" ref="I2:M139" totalsRowShown="0" headerRowCellStyle="Normal">
+  <autoFilter ref="I2:M139" xr:uid="{C46EEB7E-A7CB-C246-8ADB-5D6D5EF2C1F5}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{E1D05E23-02A1-A245-8A2F-D0E5F5388CEC}" name="priority">
-      <calculatedColumnFormula>_xlfn.XLOOKUP($J2,Table4[ward_name],Table4[priority])</calculatedColumnFormula>
+      <calculatedColumnFormula>_xlfn.XLOOKUP($J3,Table4[ward_name],Table4[priority])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{B0B7409F-D31B-A54D-A41E-85D93D215F56}" name="ward_from_turf">
-      <calculatedColumnFormula>$H2&amp;" - "&amp;$C2&amp;" - "&amp;$D2</calculatedColumnFormula>
+      <calculatedColumnFormula>$H3&amp;" - "&amp;$C3&amp;" - "&amp;$D3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{F4109E0F-477D-A140-8387-8956E6D8C0B5}" name="list_number">
-      <calculatedColumnFormula>$E2</calculatedColumnFormula>
+      <calculatedColumnFormula>$E3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{706BEE3D-B929-C744-BAA9-C6821FF738F5}" name="turf_number">
-      <calculatedColumnFormula>$F2</calculatedColumnFormula>
+      <calculatedColumnFormula>$F3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{93CE3B59-D890-9F40-ABB8-46B8574920CC}" name="door_count">
-      <calculatedColumnFormula>$G2</calculatedColumnFormula>
+      <calculatedColumnFormula>$G3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1371,11 +1383,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F1734E4D-AB22-4F42-A9F8-C159264451A0}" name="Table11" displayName="Table11" ref="N1:N138" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="N1:N138" xr:uid="{F1734E4D-AB22-4F42-A9F8-C159264451A0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F1734E4D-AB22-4F42-A9F8-C159264451A0}" name="Table11" displayName="Table11" ref="N2:N139" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="N2:N139" xr:uid="{F1734E4D-AB22-4F42-A9F8-C159264451A0}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{712C4B04-4037-B54F-8F1F-521E80419DC8}" name="duplicate_finder">
-      <calculatedColumnFormula>$J2&amp;" - "&amp;$L2</calculatedColumnFormula>
+      <calculatedColumnFormula>$J3&amp;" - "&amp;$L3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1383,13 +1395,13 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1E48B355-7F11-2A46-AEB0-F8C779ACFEC4}" name="Table4" displayName="Table4" ref="A1:C52" totalsRowShown="0" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1E48B355-7F11-2A46-AEB0-F8C779ACFEC4}" name="Table4" displayName="Table4" ref="A1:C52" totalsRowShown="0" tableBorderDxfId="7">
   <autoFilter ref="A1:C52" xr:uid="{1E48B355-7F11-2A46-AEB0-F8C779ACFEC4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FAFA12E9-D684-1A44-B71D-28D0D8D8B988}" name="priority" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{C555D931-BD11-AB4F-8893-9C69CC1CD277}" name="ward_name" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{4A3DAB92-B2D3-7A48-801E-8CD888470EDD}" name="turf_count" dataDxfId="4">
-      <calculatedColumnFormula>COUNTIF(Table7[priority],$B2)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{FAFA12E9-D684-1A44-B71D-28D0D8D8B988}" name="priority" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{C555D931-BD11-AB4F-8893-9C69CC1CD277}" name="ward_name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{4A3DAB92-B2D3-7A48-801E-8CD888470EDD}" name="turf_count" dataDxfId="0">
+      <calculatedColumnFormula>COUNTIF(Table7[ward_from_turf],$B2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1397,7 +1409,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBB29A6-220F-8A4A-96F1-FA209B57AECD}" name="Table24" displayName="Table24" ref="A1:B4" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FBB29A6-220F-8A4A-96F1-FA209B57AECD}" name="Table24" displayName="Table24" ref="A1:B4" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:B4" xr:uid="{2FBB29A6-220F-8A4A-96F1-FA209B57AECD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{C204E3BA-249A-C14A-A33A-DE02DB6DA618}" name="Misname"/>
@@ -1408,7 +1420,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F3DCD3F5-9A28-DF4D-BC83-4AA20F0FB7F2}" name="Table10" displayName="Table10" ref="A1:E138" totalsRowShown="0" headerRowDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F3DCD3F5-9A28-DF4D-BC83-4AA20F0FB7F2}" name="Table10" displayName="Table10" ref="A1:E138" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="2">
   <autoFilter ref="A1:E138" xr:uid="{F3DCD3F5-9A28-DF4D-BC83-4AA20F0FB7F2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E138">
     <sortCondition ref="A1:A138"/>
@@ -1741,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BA6C29-B237-2849-88FF-ED0F55FE0A0A}">
-  <dimension ref="A1:N138"/>
+  <dimension ref="A1:N139"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.1640625" bestFit="1" customWidth="1"/>
@@ -1762,97 +1774,60 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
+        <v>307</v>
       </c>
       <c r="H1" t="s">
-        <v>188</v>
+        <v>308</v>
       </c>
       <c r="I1" t="s">
-        <v>247</v>
-      </c>
-      <c r="J1" t="s">
-        <v>193</v>
-      </c>
-      <c r="K1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>306</v>
+        <v>309</v>
+      </c>
+      <c r="N1" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>48</v>
-      </c>
-      <c r="H2" t="str">
-        <f>_xlfn.XLOOKUP($B2,Table24[Misname],Table24[Canonical],$B2)</f>
-        <v>Stevens Point</v>
-      </c>
-      <c r="I2">
-        <f>_xlfn.XLOOKUP($J2,Table4[ward_name],Table4[priority])</f>
-        <v>44</v>
-      </c>
-      <c r="J2" t="str">
-        <f>$H2&amp;" - "&amp;$C2&amp;" - "&amp;$D2</f>
-        <v>Stevens Point - C - 0024</v>
-      </c>
-      <c r="K2" t="str">
-        <f>$E2</f>
-        <v>57880184-61293</v>
-      </c>
-      <c r="L2" t="str">
-        <f>$F2</f>
-        <v>Turf 01</v>
-      </c>
-      <c r="M2">
-        <f>$G2</f>
-        <v>48</v>
-      </c>
-      <c r="N2" t="str">
-        <f>$J2&amp;" - "&amp;$L2</f>
-        <v>Stevens Point - C - 0024 - Turf 01</v>
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -1869,13 +1844,13 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H3" t="str">
         <f>_xlfn.XLOOKUP($B3,Table24[Misname],Table24[Canonical],$B3)</f>
@@ -1886,24 +1861,24 @@
         <v>44</v>
       </c>
       <c r="J3" t="str">
-        <f>$H3&amp;" - "&amp;$C3&amp;" - "&amp;$D3</f>
+        <f t="shared" ref="J3:J34" si="0">$H3&amp;" - "&amp;$C3&amp;" - "&amp;$D3</f>
         <v>Stevens Point - C - 0024</v>
       </c>
       <c r="K3" t="str">
-        <f>$E3</f>
-        <v>57880185-21152</v>
+        <f t="shared" ref="K3:K34" si="1">$E3</f>
+        <v>57880184-61293</v>
       </c>
       <c r="L3" t="str">
-        <f>$F3</f>
-        <v>Turf 02</v>
+        <f t="shared" ref="L3:L34" si="2">$F3</f>
+        <v>Turf 01</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M66" si="0">$G3</f>
-        <v>39</v>
+        <f>$G3</f>
+        <v>48</v>
       </c>
       <c r="N3" t="str">
-        <f>$J3&amp;" - "&amp;$L3</f>
-        <v>Stevens Point - C - 0024 - Turf 02</v>
+        <f t="shared" ref="N3:N34" si="3">$J3&amp;" - "&amp;$L3</f>
+        <v>Stevens Point - C - 0024 - Turf 01</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -1920,13 +1895,13 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H4" t="str">
         <f>_xlfn.XLOOKUP($B4,Table24[Misname],Table24[Canonical],$B4)</f>
@@ -1937,75 +1912,75 @@
         <v>44</v>
       </c>
       <c r="J4" t="str">
-        <f>$H4&amp;" - "&amp;$C4&amp;" - "&amp;$D4</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0024</v>
       </c>
       <c r="K4" t="str">
-        <f>$E4</f>
-        <v>57880186-85737</v>
+        <f t="shared" si="1"/>
+        <v>57880185-21152</v>
       </c>
       <c r="L4" t="str">
-        <f>$F4</f>
-        <v>Turf 04</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M4">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <f t="shared" ref="M4:M67" si="4">$G4</f>
+        <v>39</v>
       </c>
       <c r="N4" t="str">
-        <f>$J4&amp;" - "&amp;$L4</f>
-        <v>Stevens Point - C - 0024 - Turf 04</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0024 - Turf 02</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H5" t="str">
         <f>_xlfn.XLOOKUP($B5,Table24[Misname],Table24[Canonical],$B5)</f>
-        <v>Park Ridge</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I5">
         <f>_xlfn.XLOOKUP($J5,Table4[ward_name],Table4[priority])</f>
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="J5" t="str">
-        <f>$H5&amp;" - "&amp;$C5&amp;" - "&amp;$D5</f>
-        <v>Park Ridge - V - 0001</v>
+        <f t="shared" si="0"/>
+        <v>Stevens Point - C - 0024</v>
       </c>
       <c r="K5" t="str">
-        <f>$E5</f>
-        <v>57880061-78034</v>
+        <f t="shared" si="1"/>
+        <v>57880186-85737</v>
       </c>
       <c r="L5" t="str">
-        <f>$F5</f>
-        <v>Turf 01</v>
+        <f t="shared" si="2"/>
+        <v>Turf 04</v>
       </c>
       <c r="M5">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>24</v>
       </c>
       <c r="N5" t="str">
-        <f>$J5&amp;" - "&amp;$L5</f>
-        <v>Park Ridge - V - 0001 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0024 - Turf 04</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -2022,13 +1997,13 @@
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="H6" t="str">
         <f>_xlfn.XLOOKUP($B6,Table24[Misname],Table24[Canonical],$B6)</f>
@@ -2039,24 +2014,24 @@
         <v>20</v>
       </c>
       <c r="J6" t="str">
-        <f>$H6&amp;" - "&amp;$C6&amp;" - "&amp;$D6</f>
+        <f t="shared" si="0"/>
         <v>Park Ridge - V - 0001</v>
       </c>
       <c r="K6" t="str">
-        <f>$E6</f>
-        <v>57880062-70185</v>
+        <f t="shared" si="1"/>
+        <v>57880061-78034</v>
       </c>
       <c r="L6" t="str">
-        <f>$F6</f>
-        <v>Turf 02</v>
+        <f t="shared" si="2"/>
+        <v>Turf 01</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
-        <v>58</v>
+        <f t="shared" si="4"/>
+        <v>20</v>
       </c>
       <c r="N6" t="str">
-        <f>$J6&amp;" - "&amp;$L6</f>
-        <v>Park Ridge - V - 0001 - Turf 02</v>
+        <f t="shared" si="3"/>
+        <v>Park Ridge - V - 0001 - Turf 01</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -2073,13 +2048,13 @@
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H7" t="str">
         <f>_xlfn.XLOOKUP($B7,Table24[Misname],Table24[Canonical],$B7)</f>
@@ -2090,75 +2065,75 @@
         <v>20</v>
       </c>
       <c r="J7" t="str">
-        <f>$H7&amp;" - "&amp;$C7&amp;" - "&amp;$D7</f>
+        <f t="shared" si="0"/>
         <v>Park Ridge - V - 0001</v>
       </c>
       <c r="K7" t="str">
-        <f>$E7</f>
-        <v>57880063-87752</v>
+        <f t="shared" si="1"/>
+        <v>57880062-70185</v>
       </c>
       <c r="L7" t="str">
-        <f>$F7</f>
-        <v>Turf 03</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M7">
-        <f t="shared" si="0"/>
-        <v>51</v>
+        <f t="shared" si="4"/>
+        <v>58</v>
       </c>
       <c r="N7" t="str">
-        <f>$J7&amp;" - "&amp;$L7</f>
-        <v>Park Ridge - V - 0001 - Turf 03</v>
+        <f t="shared" si="3"/>
+        <v>Park Ridge - V - 0001 - Turf 02</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H8" t="str">
         <f>_xlfn.XLOOKUP($B8,Table24[Misname],Table24[Canonical],$B8)</f>
-        <v>Plover</v>
+        <v>Park Ridge</v>
       </c>
       <c r="I8">
         <f>_xlfn.XLOOKUP($J8,Table4[ward_name],Table4[priority])</f>
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J8" t="str">
-        <f>$H8&amp;" - "&amp;$C8&amp;" - "&amp;$D8</f>
-        <v>Plover - V - 0007</v>
+        <f t="shared" si="0"/>
+        <v>Park Ridge - V - 0001</v>
       </c>
       <c r="K8" t="str">
-        <f>$E8</f>
-        <v>57880246-51319</v>
+        <f t="shared" si="1"/>
+        <v>57880063-87752</v>
       </c>
       <c r="L8" t="str">
-        <f>$F8</f>
-        <v>Turf 01</v>
+        <f t="shared" si="2"/>
+        <v>Turf 03</v>
       </c>
       <c r="M8">
-        <f t="shared" si="0"/>
-        <v>53</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="N8" t="str">
-        <f>$J8&amp;" - "&amp;$L8</f>
-        <v>Plover - V - 0007 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Park Ridge - V - 0001 - Turf 03</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -2175,13 +2150,13 @@
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H9" t="str">
         <f>_xlfn.XLOOKUP($B9,Table24[Misname],Table24[Canonical],$B9)</f>
@@ -2192,24 +2167,24 @@
         <v>46</v>
       </c>
       <c r="J9" t="str">
-        <f>$H9&amp;" - "&amp;$C9&amp;" - "&amp;$D9</f>
+        <f t="shared" si="0"/>
         <v>Plover - V - 0007</v>
       </c>
       <c r="K9" t="str">
-        <f>$E9</f>
-        <v>57880247-68885</v>
+        <f t="shared" si="1"/>
+        <v>57880246-51319</v>
       </c>
       <c r="L9" t="str">
-        <f>$F9</f>
-        <v>Turf 02</v>
+        <f t="shared" si="2"/>
+        <v>Turf 01</v>
       </c>
       <c r="M9">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f t="shared" si="4"/>
+        <v>53</v>
       </c>
       <c r="N9" t="str">
-        <f>$J9&amp;" - "&amp;$L9</f>
-        <v>Plover - V - 0007 - Turf 02</v>
+        <f t="shared" si="3"/>
+        <v>Plover - V - 0007 - Turf 01</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -2226,13 +2201,13 @@
         <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H10" t="str">
         <f>_xlfn.XLOOKUP($B10,Table24[Misname],Table24[Canonical],$B10)</f>
@@ -2243,24 +2218,24 @@
         <v>46</v>
       </c>
       <c r="J10" t="str">
-        <f>$H10&amp;" - "&amp;$C10&amp;" - "&amp;$D10</f>
+        <f t="shared" si="0"/>
         <v>Plover - V - 0007</v>
       </c>
       <c r="K10" t="str">
-        <f>$E10</f>
-        <v>57880248-86452</v>
+        <f t="shared" si="1"/>
+        <v>57880247-68885</v>
       </c>
       <c r="L10" t="str">
-        <f>$F10</f>
-        <v>Turf 03</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M10">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <f t="shared" si="4"/>
+        <v>39</v>
       </c>
       <c r="N10" t="str">
-        <f>$J10&amp;" - "&amp;$L10</f>
-        <v>Plover - V - 0007 - Turf 03</v>
+        <f t="shared" si="3"/>
+        <v>Plover - V - 0007 - Turf 02</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -2277,13 +2252,13 @@
         <v>23</v>
       </c>
       <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11">
         <v>27</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>42</v>
       </c>
       <c r="H11" t="str">
         <f>_xlfn.XLOOKUP($B11,Table24[Misname],Table24[Canonical],$B11)</f>
@@ -2294,72 +2269,75 @@
         <v>46</v>
       </c>
       <c r="J11" t="str">
-        <f>$H11&amp;" - "&amp;$C11&amp;" - "&amp;$D11</f>
+        <f t="shared" si="0"/>
         <v>Plover - V - 0007</v>
       </c>
       <c r="K11" t="str">
-        <f>$E11</f>
-        <v>57880249-14019</v>
+        <f t="shared" si="1"/>
+        <v>57880248-86452</v>
       </c>
       <c r="L11" t="str">
-        <f>$F11</f>
-        <v>Turf 04</v>
+        <f t="shared" si="2"/>
+        <v>Turf 03</v>
       </c>
       <c r="M11">
-        <f t="shared" si="0"/>
-        <v>42</v>
+        <f t="shared" si="4"/>
+        <v>27</v>
       </c>
       <c r="N11" t="str">
-        <f>$J11&amp;" - "&amp;$L11</f>
-        <v>Plover - V - 0007 - Turf 04</v>
+        <f t="shared" si="3"/>
+        <v>Plover - V - 0007 - Turf 03</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H12" t="str">
         <f>_xlfn.XLOOKUP($B12,Table24[Misname],Table24[Canonical],$B12)</f>
-        <v>Stevens Point</v>
-      </c>
-      <c r="I12" t="e">
+        <v>Plover</v>
+      </c>
+      <c r="I12">
         <f>_xlfn.XLOOKUP($J12,Table4[ward_name],Table4[priority])</f>
-        <v>#N/A</v>
+        <v>46</v>
       </c>
       <c r="J12" t="str">
-        <f>$H12&amp;" - "&amp;$C12&amp;" - "&amp;$D12</f>
-        <v>Stevens Point -  - 0017</v>
+        <f t="shared" si="0"/>
+        <v>Plover - V - 0007</v>
       </c>
       <c r="K12" t="str">
-        <f>$E12</f>
-        <v>57880209-74562</v>
+        <f t="shared" si="1"/>
+        <v>57880249-14019</v>
       </c>
       <c r="L12" t="str">
-        <f>$F12</f>
-        <v>Turf 01</v>
+        <f t="shared" si="2"/>
+        <v>Turf 04</v>
       </c>
       <c r="M12">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f t="shared" si="4"/>
+        <v>42</v>
       </c>
       <c r="N12" t="str">
-        <f>$J12&amp;" - "&amp;$L12</f>
-        <v>Stevens Point -  - 0017 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Plover - V - 0007 - Turf 04</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -2373,13 +2351,13 @@
         <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H13" t="str">
         <f>_xlfn.XLOOKUP($B13,Table24[Misname],Table24[Canonical],$B13)</f>
@@ -2390,24 +2368,24 @@
         <v>#N/A</v>
       </c>
       <c r="J13" t="str">
-        <f>$H13&amp;" - "&amp;$C13&amp;" - "&amp;$D13</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point -  - 0017</v>
       </c>
       <c r="K13" t="str">
-        <f>$E13</f>
-        <v>57880210-19695</v>
+        <f t="shared" si="1"/>
+        <v>57880209-74562</v>
       </c>
       <c r="L13" t="str">
-        <f>$F13</f>
-        <v>Turf 02</v>
+        <f t="shared" si="2"/>
+        <v>Turf 01</v>
       </c>
       <c r="M13">
-        <f t="shared" si="0"/>
-        <v>29</v>
+        <f t="shared" si="4"/>
+        <v>47</v>
       </c>
       <c r="N13" t="str">
-        <f>$J13&amp;" - "&amp;$L13</f>
-        <v>Stevens Point -  - 0017 - Turf 02</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point -  - 0017 - Turf 01</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -2421,13 +2399,13 @@
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H14" t="str">
         <f>_xlfn.XLOOKUP($B14,Table24[Misname],Table24[Canonical],$B14)</f>
@@ -2438,75 +2416,72 @@
         <v>#N/A</v>
       </c>
       <c r="J14" t="str">
-        <f>$H14&amp;" - "&amp;$C14&amp;" - "&amp;$D14</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point -  - 0017</v>
       </c>
       <c r="K14" t="str">
-        <f>$E14</f>
-        <v>57880211-11847</v>
+        <f t="shared" si="1"/>
+        <v>57880210-19695</v>
       </c>
       <c r="L14" t="str">
-        <f>$F14</f>
-        <v>Turf 03</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <f t="shared" si="4"/>
+        <v>29</v>
       </c>
       <c r="N14" t="str">
-        <f>$J14&amp;" - "&amp;$L14</f>
-        <v>Stevens Point -  - 0017 - Turf 03</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point -  - 0017 - Turf 02</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
       </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G15">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H15" t="str">
         <f>_xlfn.XLOOKUP($B15,Table24[Misname],Table24[Canonical],$B15)</f>
         <v>Stevens Point</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="e">
         <f>_xlfn.XLOOKUP($J15,Table4[ward_name],Table4[priority])</f>
-        <v>22</v>
+        <v>#N/A</v>
       </c>
       <c r="J15" t="str">
-        <f>$H15&amp;" - "&amp;$C15&amp;" - "&amp;$D15</f>
-        <v>Stevens Point - C - 0023</v>
+        <f t="shared" si="0"/>
+        <v>Stevens Point -  - 0017</v>
       </c>
       <c r="K15" t="str">
-        <f>$E15</f>
-        <v>57880093-53805</v>
+        <f t="shared" si="1"/>
+        <v>57880211-11847</v>
       </c>
       <c r="L15" t="str">
-        <f>$F15</f>
-        <v>Turf 01</v>
+        <f t="shared" si="2"/>
+        <v>Turf 03</v>
       </c>
       <c r="M15">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <f t="shared" si="4"/>
+        <v>27</v>
       </c>
       <c r="N15" t="str">
-        <f>$J15&amp;" - "&amp;$L15</f>
-        <v>Stevens Point - C - 0023 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point -  - 0017 - Turf 03</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -2523,13 +2498,13 @@
         <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H16" t="str">
         <f>_xlfn.XLOOKUP($B16,Table24[Misname],Table24[Canonical],$B16)</f>
@@ -2540,24 +2515,24 @@
         <v>22</v>
       </c>
       <c r="J16" t="str">
-        <f>$H16&amp;" - "&amp;$C16&amp;" - "&amp;$D16</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0023</v>
       </c>
       <c r="K16" t="str">
-        <f>$E16</f>
-        <v>57880094-45957</v>
+        <f t="shared" si="1"/>
+        <v>57880093-53805</v>
       </c>
       <c r="L16" t="str">
-        <f>$F16</f>
-        <v>Turf 02</v>
+        <f t="shared" si="2"/>
+        <v>Turf 01</v>
       </c>
       <c r="M16">
-        <f t="shared" si="0"/>
-        <v>34</v>
+        <f t="shared" si="4"/>
+        <v>36</v>
       </c>
       <c r="N16" t="str">
-        <f>$J16&amp;" - "&amp;$L16</f>
-        <v>Stevens Point - C - 0023 - Turf 02</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0023 - Turf 01</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -2574,13 +2549,13 @@
         <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G17">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H17" t="str">
         <f>_xlfn.XLOOKUP($B17,Table24[Misname],Table24[Canonical],$B17)</f>
@@ -2591,29 +2566,29 @@
         <v>22</v>
       </c>
       <c r="J17" t="str">
-        <f>$H17&amp;" - "&amp;$C17&amp;" - "&amp;$D17</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0023</v>
       </c>
       <c r="K17" t="str">
-        <f>$E17</f>
-        <v>57880095-81090</v>
+        <f t="shared" si="1"/>
+        <v>57880094-45957</v>
       </c>
       <c r="L17" t="str">
-        <f>$F17</f>
-        <v>Turf 03</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M17">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f t="shared" si="4"/>
+        <v>34</v>
       </c>
       <c r="N17" t="str">
-        <f>$J17&amp;" - "&amp;$L17</f>
-        <v>Stevens Point - C - 0023 - Turf 03</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0023 - Turf 02</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
@@ -2622,16 +2597,16 @@
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G18">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H18" t="str">
         <f>_xlfn.XLOOKUP($B18,Table24[Misname],Table24[Canonical],$B18)</f>
@@ -2639,27 +2614,27 @@
       </c>
       <c r="I18">
         <f>_xlfn.XLOOKUP($J18,Table4[ward_name],Table4[priority])</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J18" t="str">
-        <f>$H18&amp;" - "&amp;$C18&amp;" - "&amp;$D18</f>
-        <v>Stevens Point - C - 0028</v>
+        <f t="shared" si="0"/>
+        <v>Stevens Point - C - 0023</v>
       </c>
       <c r="K18" t="str">
-        <f>$E18</f>
-        <v>57880217-61988</v>
+        <f t="shared" si="1"/>
+        <v>57880095-81090</v>
       </c>
       <c r="L18" t="str">
-        <f>$F18</f>
-        <v>Turf 01</v>
+        <f t="shared" si="2"/>
+        <v>Turf 03</v>
       </c>
       <c r="M18">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f t="shared" si="4"/>
+        <v>38</v>
       </c>
       <c r="N18" t="str">
-        <f>$J18&amp;" - "&amp;$L18</f>
-        <v>Stevens Point - C - 0028 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0023 - Turf 03</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -2676,13 +2651,13 @@
         <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H19" t="str">
         <f>_xlfn.XLOOKUP($B19,Table24[Misname],Table24[Canonical],$B19)</f>
@@ -2693,24 +2668,24 @@
         <v>25</v>
       </c>
       <c r="J19" t="str">
-        <f>$H19&amp;" - "&amp;$C19&amp;" - "&amp;$D19</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0028</v>
       </c>
       <c r="K19" t="str">
-        <f>$E19</f>
-        <v>57880218-21847</v>
+        <f t="shared" si="1"/>
+        <v>57880217-61988</v>
       </c>
       <c r="L19" t="str">
-        <f>$F19</f>
-        <v>Turf 02</v>
+        <f t="shared" si="2"/>
+        <v>Turf 01</v>
       </c>
       <c r="M19">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f t="shared" si="4"/>
+        <v>39</v>
       </c>
       <c r="N19" t="str">
-        <f>$J19&amp;" - "&amp;$L19</f>
-        <v>Stevens Point - C - 0028 - Turf 02</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0028 - Turf 01</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -2727,13 +2702,13 @@
         <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H20" t="str">
         <f>_xlfn.XLOOKUP($B20,Table24[Misname],Table24[Canonical],$B20)</f>
@@ -2744,24 +2719,24 @@
         <v>25</v>
       </c>
       <c r="J20" t="str">
-        <f>$H20&amp;" - "&amp;$C20&amp;" - "&amp;$D20</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0028</v>
       </c>
       <c r="K20" t="str">
-        <f>$E20</f>
-        <v>57880219-56980</v>
+        <f t="shared" si="1"/>
+        <v>57880218-21847</v>
       </c>
       <c r="L20" t="str">
-        <f>$F20</f>
-        <v>Turf 03</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M20">
-        <f t="shared" si="0"/>
-        <v>48</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="N20" t="str">
-        <f>$J20&amp;" - "&amp;$L20</f>
-        <v>Stevens Point - C - 0028 - Turf 03</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0028 - Turf 02</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -2778,13 +2753,13 @@
         <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G21">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H21" t="str">
         <f>_xlfn.XLOOKUP($B21,Table24[Misname],Table24[Canonical],$B21)</f>
@@ -2795,29 +2770,29 @@
         <v>25</v>
       </c>
       <c r="J21" t="str">
-        <f>$H21&amp;" - "&amp;$C21&amp;" - "&amp;$D21</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0028</v>
       </c>
       <c r="K21" t="str">
-        <f>$E21</f>
-        <v>57880220-34406</v>
+        <f t="shared" si="1"/>
+        <v>57880219-56980</v>
       </c>
       <c r="L21" t="str">
-        <f>$F21</f>
-        <v>Turf 04</v>
+        <f t="shared" si="2"/>
+        <v>Turf 03</v>
       </c>
       <c r="M21">
-        <f t="shared" si="0"/>
-        <v>44</v>
+        <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="N21" t="str">
-        <f>$J21&amp;" - "&amp;$L21</f>
-        <v>Stevens Point - C - 0028 - Turf 04</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0028 - Turf 03</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
@@ -2826,16 +2801,16 @@
         <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G22">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H22" t="str">
         <f>_xlfn.XLOOKUP($B22,Table24[Misname],Table24[Canonical],$B22)</f>
@@ -2843,44 +2818,44 @@
       </c>
       <c r="I22">
         <f>_xlfn.XLOOKUP($J22,Table4[ward_name],Table4[priority])</f>
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J22" t="str">
-        <f>$H22&amp;" - "&amp;$C22&amp;" - "&amp;$D22</f>
-        <v>Stevens Point - C - 0007</v>
+        <f t="shared" si="0"/>
+        <v>Stevens Point - C - 0028</v>
       </c>
       <c r="K22" t="str">
-        <f>$E22</f>
-        <v>57880104-48723</v>
+        <f t="shared" si="1"/>
+        <v>57880220-34406</v>
       </c>
       <c r="L22" t="str">
-        <f>$F22</f>
-        <v>Turf 01</v>
+        <f t="shared" si="2"/>
+        <v>Turf 04</v>
       </c>
       <c r="M22">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f t="shared" si="4"/>
+        <v>44</v>
       </c>
       <c r="N22" t="str">
-        <f>$J22&amp;" - "&amp;$L22</f>
-        <v>Stevens Point - C - 0007 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0028 - Turf 04</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
         <v>10</v>
@@ -2890,31 +2865,31 @@
       </c>
       <c r="H23" t="str">
         <f>_xlfn.XLOOKUP($B23,Table24[Misname],Table24[Canonical],$B23)</f>
-        <v>Whiting</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I23">
         <f>_xlfn.XLOOKUP($J23,Table4[ward_name],Table4[priority])</f>
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J23" t="str">
-        <f>$H23&amp;" - "&amp;$C23&amp;" - "&amp;$D23</f>
-        <v>Whiting - V - 0002</v>
+        <f t="shared" si="0"/>
+        <v>Stevens Point - C - 0007</v>
       </c>
       <c r="K23" t="str">
-        <f>$E23</f>
-        <v>57880214-28528</v>
+        <f t="shared" si="1"/>
+        <v>57880104-48723</v>
       </c>
       <c r="L23" t="str">
-        <f>$F23</f>
+        <f t="shared" si="2"/>
         <v>Turf 01</v>
       </c>
       <c r="M23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>47</v>
       </c>
       <c r="N23" t="str">
-        <f>$J23&amp;" - "&amp;$L23</f>
-        <v>Whiting - V - 0002 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0007 - Turf 01</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -2931,13 +2906,13 @@
         <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H24" t="str">
         <f>_xlfn.XLOOKUP($B24,Table24[Misname],Table24[Canonical],$B24)</f>
@@ -2948,24 +2923,24 @@
         <v>35</v>
       </c>
       <c r="J24" t="str">
-        <f>$H24&amp;" - "&amp;$C24&amp;" - "&amp;$D24</f>
+        <f t="shared" si="0"/>
         <v>Whiting - V - 0002</v>
       </c>
       <c r="K24" t="str">
-        <f>$E24</f>
-        <v>57880215-78387</v>
+        <f t="shared" si="1"/>
+        <v>57880214-28528</v>
       </c>
       <c r="L24" t="str">
-        <f>$F24</f>
-        <v>Turf 02</v>
+        <f t="shared" si="2"/>
+        <v>Turf 01</v>
       </c>
       <c r="M24">
-        <f t="shared" si="0"/>
-        <v>33</v>
+        <f t="shared" si="4"/>
+        <v>47</v>
       </c>
       <c r="N24" t="str">
-        <f>$J24&amp;" - "&amp;$L24</f>
-        <v>Whiting - V - 0002 - Turf 02</v>
+        <f t="shared" si="3"/>
+        <v>Whiting - V - 0002 - Turf 01</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -2982,13 +2957,13 @@
         <v>43</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G25">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H25" t="str">
         <f>_xlfn.XLOOKUP($B25,Table24[Misname],Table24[Canonical],$B25)</f>
@@ -2999,75 +2974,75 @@
         <v>35</v>
       </c>
       <c r="J25" t="str">
-        <f>$H25&amp;" - "&amp;$C25&amp;" - "&amp;$D25</f>
+        <f t="shared" si="0"/>
         <v>Whiting - V - 0002</v>
       </c>
       <c r="K25" t="str">
-        <f>$E25</f>
-        <v>57880216-95954</v>
+        <f t="shared" si="1"/>
+        <v>57880215-78387</v>
       </c>
       <c r="L25" t="str">
-        <f>$F25</f>
-        <v>Turf 03</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M25">
-        <f t="shared" si="0"/>
-        <v>37</v>
+        <f t="shared" si="4"/>
+        <v>33</v>
       </c>
       <c r="N25" t="str">
-        <f>$J25&amp;" - "&amp;$L25</f>
-        <v>Whiting - V - 0002 - Turf 03</v>
+        <f t="shared" si="3"/>
+        <v>Whiting - V - 0002 - Turf 02</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G26">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H26" t="str">
         <f>_xlfn.XLOOKUP($B26,Table24[Misname],Table24[Canonical],$B26)</f>
-        <v>Stevens Point</v>
+        <v>Whiting</v>
       </c>
       <c r="I26">
         <f>_xlfn.XLOOKUP($J26,Table4[ward_name],Table4[priority])</f>
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="J26" t="str">
-        <f>$H26&amp;" - "&amp;$C26&amp;" - "&amp;$D26</f>
-        <v>Stevens Point - C - 0001</v>
+        <f t="shared" si="0"/>
+        <v>Whiting - V - 0002</v>
       </c>
       <c r="K26" t="str">
-        <f>$E26</f>
-        <v>57880270-66137</v>
+        <f t="shared" si="1"/>
+        <v>57880216-95954</v>
       </c>
       <c r="L26" t="str">
-        <f>$F26</f>
-        <v>Turf 01</v>
+        <f t="shared" si="2"/>
+        <v>Turf 03</v>
       </c>
       <c r="M26">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f t="shared" si="4"/>
+        <v>37</v>
       </c>
       <c r="N26" t="str">
-        <f>$J26&amp;" - "&amp;$L26</f>
-        <v>Stevens Point - C - 0001 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Whiting - V - 0002 - Turf 03</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -3084,13 +3059,13 @@
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H27" t="str">
         <f>_xlfn.XLOOKUP($B27,Table24[Misname],Table24[Canonical],$B27)</f>
@@ -3101,24 +3076,24 @@
         <v>5</v>
       </c>
       <c r="J27" t="str">
-        <f>$H27&amp;" - "&amp;$C27&amp;" - "&amp;$D27</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0001</v>
       </c>
       <c r="K27" t="str">
-        <f>$E27</f>
-        <v>57880271-83704</v>
+        <f t="shared" si="1"/>
+        <v>57880270-66137</v>
       </c>
       <c r="L27" t="str">
-        <f>$F27</f>
-        <v>Turf 02</v>
+        <f t="shared" si="2"/>
+        <v>Turf 01</v>
       </c>
       <c r="M27">
-        <f t="shared" si="0"/>
-        <v>51</v>
+        <f t="shared" si="4"/>
+        <v>32</v>
       </c>
       <c r="N27" t="str">
-        <f>$J27&amp;" - "&amp;$L27</f>
-        <v>Stevens Point - C - 0001 - Turf 02</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0001 - Turf 01</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -3135,13 +3110,13 @@
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G28">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H28" t="str">
         <f>_xlfn.XLOOKUP($B28,Table24[Misname],Table24[Canonical],$B28)</f>
@@ -3152,47 +3127,47 @@
         <v>5</v>
       </c>
       <c r="J28" t="str">
-        <f>$H28&amp;" - "&amp;$C28&amp;" - "&amp;$D28</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0001</v>
       </c>
       <c r="K28" t="str">
-        <f>$E28</f>
-        <v>57880272-11271</v>
+        <f t="shared" si="1"/>
+        <v>57880271-83704</v>
       </c>
       <c r="L28" t="str">
-        <f>$F28</f>
-        <v>Turf 03</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M28">
-        <f t="shared" si="0"/>
-        <v>49</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="N28" t="str">
-        <f>$J28&amp;" - "&amp;$L28</f>
-        <v>Stevens Point - C - 0001 - Turf 03</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0001 - Turf 02</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G29">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H29" t="str">
         <f>_xlfn.XLOOKUP($B29,Table24[Misname],Table24[Canonical],$B29)</f>
@@ -3200,27 +3175,27 @@
       </c>
       <c r="I29">
         <f>_xlfn.XLOOKUP($J29,Table4[ward_name],Table4[priority])</f>
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="J29" t="str">
-        <f>$H29&amp;" - "&amp;$C29&amp;" - "&amp;$D29</f>
-        <v>Stevens Point - C - 0020</v>
+        <f t="shared" si="0"/>
+        <v>Stevens Point - C - 0001</v>
       </c>
       <c r="K29" t="str">
-        <f>$E29</f>
-        <v>57880100-38788</v>
+        <f t="shared" si="1"/>
+        <v>57880272-11271</v>
       </c>
       <c r="L29" t="str">
-        <f>$F29</f>
-        <v>Turf 01</v>
+        <f t="shared" si="2"/>
+        <v>Turf 03</v>
       </c>
       <c r="M29">
-        <f t="shared" si="0"/>
-        <v>44</v>
+        <f t="shared" si="4"/>
+        <v>49</v>
       </c>
       <c r="N29" t="str">
-        <f>$J29&amp;" - "&amp;$L29</f>
-        <v>Stevens Point - C - 0020 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0001 - Turf 03</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -3237,13 +3212,13 @@
         <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H30" t="str">
         <f>_xlfn.XLOOKUP($B30,Table24[Misname],Table24[Canonical],$B30)</f>
@@ -3254,24 +3229,24 @@
         <v>31</v>
       </c>
       <c r="J30" t="str">
-        <f>$H30&amp;" - "&amp;$C30&amp;" - "&amp;$D30</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0020</v>
       </c>
       <c r="K30" t="str">
-        <f>$E30</f>
-        <v>57880101-51347</v>
+        <f t="shared" si="1"/>
+        <v>57880100-38788</v>
       </c>
       <c r="L30" t="str">
-        <f>$F30</f>
-        <v>Turf 02</v>
+        <f t="shared" si="2"/>
+        <v>Turf 01</v>
       </c>
       <c r="M30">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f t="shared" si="4"/>
+        <v>44</v>
       </c>
       <c r="N30" t="str">
-        <f>$J30&amp;" - "&amp;$L30</f>
-        <v>Stevens Point - C - 0020 - Turf 02</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0020 - Turf 01</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -3288,13 +3263,13 @@
         <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G31">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H31" t="str">
         <f>_xlfn.XLOOKUP($B31,Table24[Misname],Table24[Canonical],$B31)</f>
@@ -3305,47 +3280,47 @@
         <v>31</v>
       </c>
       <c r="J31" t="str">
-        <f>$H31&amp;" - "&amp;$C31&amp;" - "&amp;$D31</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0020</v>
       </c>
       <c r="K31" t="str">
-        <f>$E31</f>
-        <v>57880102-25932</v>
+        <f t="shared" si="1"/>
+        <v>57880101-51347</v>
       </c>
       <c r="L31" t="str">
-        <f>$F31</f>
-        <v>Turf 03</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M31">
-        <f t="shared" si="0"/>
-        <v>42</v>
+        <f t="shared" si="4"/>
+        <v>38</v>
       </c>
       <c r="N31" t="str">
-        <f>$J31&amp;" - "&amp;$L31</f>
-        <v>Stevens Point - C - 0020 - Turf 03</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0020 - Turf 02</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G32">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H32" t="str">
         <f>_xlfn.XLOOKUP($B32,Table24[Misname],Table24[Canonical],$B32)</f>
@@ -3353,27 +3328,27 @@
       </c>
       <c r="I32">
         <f>_xlfn.XLOOKUP($J32,Table4[ward_name],Table4[priority])</f>
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="J32" t="str">
-        <f>$H32&amp;" - "&amp;$C32&amp;" - "&amp;$D32</f>
-        <v>Stevens Point - C - 0014</v>
+        <f t="shared" si="0"/>
+        <v>Stevens Point - C - 0020</v>
       </c>
       <c r="K32" t="str">
-        <f>$E32</f>
-        <v>57880288-54186</v>
+        <f t="shared" si="1"/>
+        <v>57880102-25932</v>
       </c>
       <c r="L32" t="str">
-        <f>$F32</f>
-        <v>Turf 01</v>
+        <f t="shared" si="2"/>
+        <v>Turf 03</v>
       </c>
       <c r="M32">
-        <f t="shared" si="0"/>
-        <v>46</v>
+        <f t="shared" si="4"/>
+        <v>42</v>
       </c>
       <c r="N32" t="str">
-        <f>$J32&amp;" - "&amp;$L32</f>
-        <v>Stevens Point - C - 0014 - Turf 01</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0020 - Turf 03</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -3390,13 +3365,13 @@
         <v>55</v>
       </c>
       <c r="E33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H33" t="str">
         <f>_xlfn.XLOOKUP($B33,Table24[Misname],Table24[Canonical],$B33)</f>
@@ -3407,24 +3382,24 @@
         <v>7</v>
       </c>
       <c r="J33" t="str">
-        <f>$H33&amp;" - "&amp;$C33&amp;" - "&amp;$D33</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0014</v>
       </c>
       <c r="K33" t="str">
-        <f>$E33</f>
-        <v>57880289-71752</v>
+        <f t="shared" si="1"/>
+        <v>57880288-54186</v>
       </c>
       <c r="L33" t="str">
-        <f>$F33</f>
-        <v>Turf 02</v>
+        <f t="shared" si="2"/>
+        <v>Turf 01</v>
       </c>
       <c r="M33">
-        <f t="shared" si="0"/>
-        <v>41</v>
+        <f t="shared" si="4"/>
+        <v>46</v>
       </c>
       <c r="N33" t="str">
-        <f>$J33&amp;" - "&amp;$L33</f>
-        <v>Stevens Point - C - 0014 - Turf 02</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0014 - Turf 01</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -3441,13 +3416,13 @@
         <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G34">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H34" t="str">
         <f>_xlfn.XLOOKUP($B34,Table24[Misname],Table24[Canonical],$B34)</f>
@@ -3458,24 +3433,24 @@
         <v>7</v>
       </c>
       <c r="J34" t="str">
-        <f>$H34&amp;" - "&amp;$C34&amp;" - "&amp;$D34</f>
+        <f t="shared" si="0"/>
         <v>Stevens Point - C - 0014</v>
       </c>
       <c r="K34" t="str">
-        <f>$E34</f>
-        <v>57880291-89319</v>
+        <f t="shared" si="1"/>
+        <v>57880289-71752</v>
       </c>
       <c r="L34" t="str">
-        <f>$F34</f>
-        <v>Turf 03</v>
+        <f t="shared" si="2"/>
+        <v>Turf 02</v>
       </c>
       <c r="M34">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f t="shared" si="4"/>
+        <v>41</v>
       </c>
       <c r="N34" t="str">
-        <f>$J34&amp;" - "&amp;$L34</f>
-        <v>Stevens Point - C - 0014 - Turf 03</v>
+        <f t="shared" si="3"/>
+        <v>Stevens Point - C - 0014 - Turf 02</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -3492,13 +3467,13 @@
         <v>55</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G35">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H35" t="str">
         <f>_xlfn.XLOOKUP($B35,Table24[Misname],Table24[Canonical],$B35)</f>
@@ -3509,47 +3484,47 @@
         <v>7</v>
       </c>
       <c r="J35" t="str">
-        <f>$H35&amp;" - "&amp;$C35&amp;" - "&amp;$D35</f>
+        <f t="shared" ref="J35:J66" si="5">$H35&amp;" - "&amp;$C35&amp;" - "&amp;$D35</f>
         <v>Stevens Point - C - 0014</v>
       </c>
       <c r="K35" t="str">
-        <f>$E35</f>
-        <v>57880294-63904</v>
+        <f t="shared" ref="K35:K66" si="6">$E35</f>
+        <v>57880291-89319</v>
       </c>
       <c r="L35" t="str">
-        <f>$F35</f>
-        <v>Turf 04</v>
+        <f t="shared" ref="L35:L66" si="7">$F35</f>
+        <v>Turf 03</v>
       </c>
       <c r="M35">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <f t="shared" si="4"/>
+        <v>39</v>
       </c>
       <c r="N35" t="str">
-        <f>$J35&amp;" - "&amp;$L35</f>
-        <v>Stevens Point - C - 0014 - Turf 04</v>
+        <f t="shared" ref="N35:N66" si="8">$J35&amp;" - "&amp;$L35</f>
+        <v>Stevens Point - C - 0014 - Turf 03</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G36">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="H36" t="str">
         <f>_xlfn.XLOOKUP($B36,Table24[Misname],Table24[Canonical],$B36)</f>
@@ -3557,27 +3532,27 @@
       </c>
       <c r="I36">
         <f>_xlfn.XLOOKUP($J36,Table4[ward_name],Table4[priority])</f>
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J36" t="str">
-        <f>$H36&amp;" - "&amp;$C36&amp;" - "&amp;$D36</f>
-        <v>Stevens Point - C - 0026</v>
+        <f t="shared" si="5"/>
+        <v>Stevens Point - C - 0014</v>
       </c>
       <c r="K36" t="str">
-        <f>$E36</f>
-        <v>57880234-72603</v>
+        <f t="shared" si="6"/>
+        <v>57880294-63904</v>
       </c>
       <c r="L36" t="str">
-        <f>$F36</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 04</v>
       </c>
       <c r="M36">
-        <f t="shared" si="0"/>
-        <v>58</v>
+        <f t="shared" si="4"/>
+        <v>28</v>
       </c>
       <c r="N36" t="str">
-        <f>$J36&amp;" - "&amp;$L36</f>
-        <v>Stevens Point - C - 0026 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0014 - Turf 04</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -3594,13 +3569,13 @@
         <v>60</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F37" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G37">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H37" t="str">
         <f>_xlfn.XLOOKUP($B37,Table24[Misname],Table24[Canonical],$B37)</f>
@@ -3611,24 +3586,24 @@
         <v>26</v>
       </c>
       <c r="J37" t="str">
-        <f>$H37&amp;" - "&amp;$C37&amp;" - "&amp;$D37</f>
+        <f t="shared" si="5"/>
         <v>Stevens Point - C - 0026</v>
       </c>
       <c r="K37" t="str">
-        <f>$E37</f>
-        <v>57880235-90169</v>
+        <f t="shared" si="6"/>
+        <v>57880234-72603</v>
       </c>
       <c r="L37" t="str">
-        <f>$F37</f>
-        <v>Turf 03</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M37">
-        <f t="shared" si="0"/>
-        <v>61</v>
+        <f t="shared" si="4"/>
+        <v>58</v>
       </c>
       <c r="N37" t="str">
-        <f>$J37&amp;" - "&amp;$L37</f>
-        <v>Stevens Point - C - 0026 - Turf 03</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0026 - Turf 01</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
@@ -3645,13 +3620,13 @@
         <v>60</v>
       </c>
       <c r="E38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G38">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H38" t="str">
         <f>_xlfn.XLOOKUP($B38,Table24[Misname],Table24[Canonical],$B38)</f>
@@ -3662,24 +3637,24 @@
         <v>26</v>
       </c>
       <c r="J38" t="str">
-        <f>$H38&amp;" - "&amp;$C38&amp;" - "&amp;$D38</f>
+        <f t="shared" si="5"/>
         <v>Stevens Point - C - 0026</v>
       </c>
       <c r="K38" t="str">
-        <f>$E38</f>
-        <v>57880236-50028</v>
+        <f t="shared" si="6"/>
+        <v>57880235-90169</v>
       </c>
       <c r="L38" t="str">
-        <f>$F38</f>
-        <v>Turf 04</v>
+        <f t="shared" si="7"/>
+        <v>Turf 03</v>
       </c>
       <c r="M38">
-        <f t="shared" si="0"/>
-        <v>55</v>
+        <f t="shared" si="4"/>
+        <v>61</v>
       </c>
       <c r="N38" t="str">
-        <f>$J38&amp;" - "&amp;$L38</f>
-        <v>Stevens Point - C - 0026 - Turf 04</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0026 - Turf 03</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
@@ -3696,13 +3671,13 @@
         <v>60</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="G39">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H39" t="str">
         <f>_xlfn.XLOOKUP($B39,Table24[Misname],Table24[Canonical],$B39)</f>
@@ -3713,29 +3688,29 @@
         <v>26</v>
       </c>
       <c r="J39" t="str">
-        <f>$H39&amp;" - "&amp;$C39&amp;" - "&amp;$D39</f>
+        <f t="shared" si="5"/>
         <v>Stevens Point - C - 0026</v>
       </c>
       <c r="K39" t="str">
-        <f>$E39</f>
-        <v>57880237-42180</v>
+        <f t="shared" si="6"/>
+        <v>57880236-50028</v>
       </c>
       <c r="L39" t="str">
-        <f>$F39</f>
-        <v>Turf 05</v>
+        <f t="shared" si="7"/>
+        <v>Turf 04</v>
       </c>
       <c r="M39">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f t="shared" si="4"/>
+        <v>55</v>
       </c>
       <c r="N39" t="str">
-        <f>$J39&amp;" - "&amp;$L39</f>
-        <v>Stevens Point - C - 0026 - Turf 05</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0026 - Turf 04</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -3744,16 +3719,16 @@
         <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G40">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H40" t="str">
         <f>_xlfn.XLOOKUP($B40,Table24[Misname],Table24[Canonical],$B40)</f>
@@ -3761,27 +3736,27 @@
       </c>
       <c r="I40">
         <f>_xlfn.XLOOKUP($J40,Table4[ward_name],Table4[priority])</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J40" t="str">
-        <f>$H40&amp;" - "&amp;$C40&amp;" - "&amp;$D40</f>
-        <v>Stevens Point - C - 0018</v>
+        <f t="shared" si="5"/>
+        <v>Stevens Point - C - 0026</v>
       </c>
       <c r="K40" t="str">
-        <f>$E40</f>
-        <v>57880148-77275</v>
+        <f t="shared" si="6"/>
+        <v>57880237-42180</v>
       </c>
       <c r="L40" t="str">
-        <f>$F40</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 05</v>
       </c>
       <c r="M40">
-        <f t="shared" si="0"/>
-        <v>44</v>
+        <f t="shared" si="4"/>
+        <v>38</v>
       </c>
       <c r="N40" t="str">
-        <f>$J40&amp;" - "&amp;$L40</f>
-        <v>Stevens Point - C - 0018 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0026 - Turf 05</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -3798,13 +3773,13 @@
         <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G41">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H41" t="str">
         <f>_xlfn.XLOOKUP($B41,Table24[Misname],Table24[Canonical],$B41)</f>
@@ -3815,24 +3790,24 @@
         <v>23</v>
       </c>
       <c r="J41" t="str">
-        <f>$H41&amp;" - "&amp;$C41&amp;" - "&amp;$D41</f>
+        <f t="shared" si="5"/>
         <v>Stevens Point - C - 0018</v>
       </c>
       <c r="K41" t="str">
-        <f>$E41</f>
-        <v>57880149-22408</v>
+        <f t="shared" si="6"/>
+        <v>57880148-77275</v>
       </c>
       <c r="L41" t="str">
-        <f>$F41</f>
-        <v>Turf 02</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M41">
-        <f t="shared" si="0"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>44</v>
       </c>
       <c r="N41" t="str">
-        <f>$J41&amp;" - "&amp;$L41</f>
-        <v>Stevens Point - C - 0018 - Turf 02</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0018 - Turf 01</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -3849,13 +3824,13 @@
         <v>66</v>
       </c>
       <c r="E42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G42">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H42" t="str">
         <f>_xlfn.XLOOKUP($B42,Table24[Misname],Table24[Canonical],$B42)</f>
@@ -3866,24 +3841,24 @@
         <v>23</v>
       </c>
       <c r="J42" t="str">
-        <f>$H42&amp;" - "&amp;$C42&amp;" - "&amp;$D42</f>
+        <f t="shared" si="5"/>
         <v>Stevens Point - C - 0018</v>
       </c>
       <c r="K42" t="str">
-        <f>$E42</f>
-        <v>57880150-72267</v>
+        <f t="shared" si="6"/>
+        <v>57880149-22408</v>
       </c>
       <c r="L42" t="str">
-        <f>$F42</f>
-        <v>Turf 03</v>
+        <f t="shared" si="7"/>
+        <v>Turf 02</v>
       </c>
       <c r="M42">
-        <f t="shared" si="0"/>
-        <v>41</v>
+        <f t="shared" si="4"/>
+        <v>43</v>
       </c>
       <c r="N42" t="str">
-        <f>$J42&amp;" - "&amp;$L42</f>
-        <v>Stevens Point - C - 0018 - Turf 03</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0018 - Turf 02</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -3900,13 +3875,13 @@
         <v>66</v>
       </c>
       <c r="E43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G43">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H43" t="str">
         <f>_xlfn.XLOOKUP($B43,Table24[Misname],Table24[Canonical],$B43)</f>
@@ -3917,29 +3892,29 @@
         <v>23</v>
       </c>
       <c r="J43" t="str">
-        <f>$H43&amp;" - "&amp;$C43&amp;" - "&amp;$D43</f>
+        <f t="shared" si="5"/>
         <v>Stevens Point - C - 0018</v>
       </c>
       <c r="K43" t="str">
-        <f>$E43</f>
-        <v>57880151-64419</v>
+        <f t="shared" si="6"/>
+        <v>57880150-72267</v>
       </c>
       <c r="L43" t="str">
-        <f>$F43</f>
-        <v>Turf 04</v>
+        <f t="shared" si="7"/>
+        <v>Turf 03</v>
       </c>
       <c r="M43">
-        <f t="shared" si="0"/>
-        <v>35</v>
+        <f t="shared" si="4"/>
+        <v>41</v>
       </c>
       <c r="N43" t="str">
-        <f>$J43&amp;" - "&amp;$L43</f>
-        <v>Stevens Point - C - 0018 - Turf 04</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0018 - Turf 03</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B44" t="s">
         <v>6</v>
@@ -3948,16 +3923,16 @@
         <v>7</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G44">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H44" t="str">
         <f>_xlfn.XLOOKUP($B44,Table24[Misname],Table24[Canonical],$B44)</f>
@@ -3965,27 +3940,27 @@
       </c>
       <c r="I44">
         <f>_xlfn.XLOOKUP($J44,Table4[ward_name],Table4[priority])</f>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J44" t="str">
-        <f>$H44&amp;" - "&amp;$C44&amp;" - "&amp;$D44</f>
-        <v>Stevens Point - C - 0010</v>
+        <f t="shared" si="5"/>
+        <v>Stevens Point - C - 0018</v>
       </c>
       <c r="K44" t="str">
-        <f>$E44</f>
-        <v>57880053-11875</v>
+        <f t="shared" si="6"/>
+        <v>57880151-64419</v>
       </c>
       <c r="L44" t="str">
-        <f>$F44</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 04</v>
       </c>
       <c r="M44">
-        <f t="shared" si="0"/>
-        <v>43</v>
+        <f t="shared" si="4"/>
+        <v>35</v>
       </c>
       <c r="N44" t="str">
-        <f>$J44&amp;" - "&amp;$L44</f>
-        <v>Stevens Point - C - 0010 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0018 - Turf 04</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -4002,13 +3977,13 @@
         <v>71</v>
       </c>
       <c r="E45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G45">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H45" t="str">
         <f>_xlfn.XLOOKUP($B45,Table24[Misname],Table24[Canonical],$B45)</f>
@@ -4019,29 +3994,29 @@
         <v>3</v>
       </c>
       <c r="J45" t="str">
-        <f>$H45&amp;" - "&amp;$C45&amp;" - "&amp;$D45</f>
+        <f t="shared" si="5"/>
         <v>Stevens Point - C - 0010</v>
       </c>
       <c r="K45" t="str">
-        <f>$E45</f>
-        <v>57880054-76460</v>
+        <f t="shared" si="6"/>
+        <v>57880053-11875</v>
       </c>
       <c r="L45" t="str">
-        <f>$F45</f>
-        <v>Turf 02</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M45">
-        <f t="shared" si="0"/>
-        <v>33</v>
+        <f t="shared" si="4"/>
+        <v>43</v>
       </c>
       <c r="N45" t="str">
-        <f>$J45&amp;" - "&amp;$L45</f>
-        <v>Stevens Point - C - 0010 - Turf 02</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0010 - Turf 01</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B46" t="s">
         <v>6</v>
@@ -4050,16 +4025,16 @@
         <v>7</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E46" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G46">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H46" t="str">
         <f>_xlfn.XLOOKUP($B46,Table24[Misname],Table24[Canonical],$B46)</f>
@@ -4067,129 +4042,129 @@
       </c>
       <c r="I46">
         <f>_xlfn.XLOOKUP($J46,Table4[ward_name],Table4[priority])</f>
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J46" t="str">
-        <f>$H46&amp;" - "&amp;$C46&amp;" - "&amp;$D46</f>
-        <v>Stevens Point - C - 0027</v>
+        <f t="shared" si="5"/>
+        <v>Stevens Point - C - 0010</v>
       </c>
       <c r="K46" t="str">
-        <f>$E46</f>
-        <v>57880238-63290</v>
+        <f t="shared" si="6"/>
+        <v>57880054-76460</v>
       </c>
       <c r="L46" t="str">
-        <f>$F46</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 02</v>
       </c>
       <c r="M46">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f t="shared" si="4"/>
+        <v>33</v>
       </c>
       <c r="N46" t="str">
-        <f>$J46&amp;" - "&amp;$L46</f>
-        <v>Stevens Point - C - 0027 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0010 - Turf 02</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F47" t="s">
         <v>10</v>
       </c>
       <c r="G47">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="H47" t="str">
         <f>_xlfn.XLOOKUP($B47,Table24[Misname],Table24[Canonical],$B47)</f>
-        <v>Hull</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I47">
         <f>_xlfn.XLOOKUP($J47,Table4[ward_name],Table4[priority])</f>
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="J47" t="str">
-        <f>$H47&amp;" - "&amp;$C47&amp;" - "&amp;$D47</f>
-        <v>Hull - T - 0008</v>
+        <f t="shared" si="5"/>
+        <v>Stevens Point - C - 0027</v>
       </c>
       <c r="K47" t="str">
-        <f>$E47</f>
-        <v>57880068-40840</v>
+        <f t="shared" si="6"/>
+        <v>57880238-63290</v>
       </c>
       <c r="L47" t="str">
-        <f>$F47</f>
+        <f t="shared" si="7"/>
         <v>Turf 01</v>
       </c>
       <c r="M47">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <f t="shared" si="4"/>
+        <v>47</v>
       </c>
       <c r="N47" t="str">
-        <f>$J47&amp;" - "&amp;$L47</f>
-        <v>Hull - T - 0008 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0027 - Turf 01</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E48" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F48" t="s">
         <v>10</v>
       </c>
       <c r="G48">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H48" t="str">
         <f>_xlfn.XLOOKUP($B48,Table24[Misname],Table24[Canonical],$B48)</f>
-        <v>Plover</v>
+        <v>Hull</v>
       </c>
       <c r="I48">
         <f>_xlfn.XLOOKUP($J48,Table4[ward_name],Table4[priority])</f>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J48" t="str">
-        <f>$H48&amp;" - "&amp;$C48&amp;" - "&amp;$D48</f>
-        <v>Plover - V - 0004</v>
+        <f t="shared" si="5"/>
+        <v>Hull - T - 0008</v>
       </c>
       <c r="K48" t="str">
-        <f>$E48</f>
-        <v>57880135-32417</v>
+        <f t="shared" si="6"/>
+        <v>57880068-40840</v>
       </c>
       <c r="L48" t="str">
-        <f>$F48</f>
+        <f t="shared" si="7"/>
         <v>Turf 01</v>
       </c>
       <c r="M48">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <f t="shared" si="4"/>
+        <v>22</v>
       </c>
       <c r="N48" t="str">
-        <f>$J48&amp;" - "&amp;$L48</f>
-        <v>Plover - V - 0004 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Hull - T - 0008 - Turf 01</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
@@ -4206,10 +4181,10 @@
         <v>80</v>
       </c>
       <c r="E49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G49">
         <v>36</v>
@@ -4223,24 +4198,24 @@
         <v>51</v>
       </c>
       <c r="J49" t="str">
-        <f>$H49&amp;" - "&amp;$C49&amp;" - "&amp;$D49</f>
+        <f t="shared" si="5"/>
         <v>Plover - V - 0004</v>
       </c>
       <c r="K49" t="str">
-        <f>$E49</f>
-        <v>57880137-24568</v>
+        <f t="shared" si="6"/>
+        <v>57880135-32417</v>
       </c>
       <c r="L49" t="str">
-        <f>$F49</f>
-        <v>Turf 02</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="N49" t="str">
-        <f>$J49&amp;" - "&amp;$L49</f>
-        <v>Plover - V - 0004 - Turf 02</v>
+        <f t="shared" si="8"/>
+        <v>Plover - V - 0004 - Turf 01</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
@@ -4257,13 +4232,13 @@
         <v>80</v>
       </c>
       <c r="E50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F50" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G50">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H50" t="str">
         <f>_xlfn.XLOOKUP($B50,Table24[Misname],Table24[Canonical],$B50)</f>
@@ -4274,24 +4249,24 @@
         <v>51</v>
       </c>
       <c r="J50" t="str">
-        <f>$H50&amp;" - "&amp;$C50&amp;" - "&amp;$D50</f>
+        <f t="shared" si="5"/>
         <v>Plover - V - 0004</v>
       </c>
       <c r="K50" t="str">
-        <f>$E50</f>
-        <v>57880139-91994</v>
+        <f t="shared" si="6"/>
+        <v>57880137-24568</v>
       </c>
       <c r="L50" t="str">
-        <f>$F50</f>
-        <v>Turf 03</v>
+        <f t="shared" si="7"/>
+        <v>Turf 02</v>
       </c>
       <c r="M50">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f t="shared" si="4"/>
+        <v>36</v>
       </c>
       <c r="N50" t="str">
-        <f>$J50&amp;" - "&amp;$L50</f>
-        <v>Plover - V - 0004 - Turf 03</v>
+        <f t="shared" si="8"/>
+        <v>Plover - V - 0004 - Turf 02</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
@@ -4308,13 +4283,13 @@
         <v>80</v>
       </c>
       <c r="E51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G51">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H51" t="str">
         <f>_xlfn.XLOOKUP($B51,Table24[Misname],Table24[Canonical],$B51)</f>
@@ -4325,24 +4300,24 @@
         <v>51</v>
       </c>
       <c r="J51" t="str">
-        <f>$H51&amp;" - "&amp;$C51&amp;" - "&amp;$D51</f>
+        <f t="shared" si="5"/>
         <v>Plover - V - 0004</v>
       </c>
       <c r="K51" t="str">
-        <f>$E51</f>
-        <v>57880141-84145</v>
+        <f t="shared" si="6"/>
+        <v>57880139-91994</v>
       </c>
       <c r="L51" t="str">
-        <f>$F51</f>
-        <v>Turf 04</v>
+        <f t="shared" si="7"/>
+        <v>Turf 03</v>
       </c>
       <c r="M51">
-        <f t="shared" si="0"/>
-        <v>42</v>
+        <f t="shared" si="4"/>
+        <v>39</v>
       </c>
       <c r="N51" t="str">
-        <f>$J51&amp;" - "&amp;$L51</f>
-        <v>Plover - V - 0004 - Turf 04</v>
+        <f t="shared" si="8"/>
+        <v>Plover - V - 0004 - Turf 03</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
@@ -4359,13 +4334,13 @@
         <v>80</v>
       </c>
       <c r="E52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F52" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="G52">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H52" t="str">
         <f>_xlfn.XLOOKUP($B52,Table24[Misname],Table24[Canonical],$B52)</f>
@@ -4376,75 +4351,75 @@
         <v>51</v>
       </c>
       <c r="J52" t="str">
-        <f>$H52&amp;" - "&amp;$C52&amp;" - "&amp;$D52</f>
+        <f t="shared" si="5"/>
         <v>Plover - V - 0004</v>
       </c>
       <c r="K52" t="str">
-        <f>$E52</f>
-        <v>57880143-61571</v>
+        <f t="shared" si="6"/>
+        <v>57880141-84145</v>
       </c>
       <c r="L52" t="str">
-        <f>$F52</f>
-        <v>Turf 05</v>
+        <f t="shared" si="7"/>
+        <v>Turf 04</v>
       </c>
       <c r="M52">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f t="shared" si="4"/>
+        <v>42</v>
       </c>
       <c r="N52" t="str">
-        <f>$J52&amp;" - "&amp;$L52</f>
-        <v>Plover - V - 0004 - Turf 05</v>
+        <f t="shared" si="8"/>
+        <v>Plover - V - 0004 - Turf 04</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C53" t="s">
         <v>16</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="E53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F53" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G53">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H53" t="str">
         <f>_xlfn.XLOOKUP($B53,Table24[Misname],Table24[Canonical],$B53)</f>
-        <v>Whiting</v>
+        <v>Plover</v>
       </c>
       <c r="I53">
         <f>_xlfn.XLOOKUP($J53,Table4[ward_name],Table4[priority])</f>
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J53" t="str">
-        <f>$H53&amp;" - "&amp;$C53&amp;" - "&amp;$D53</f>
-        <v>Whiting - V - 0001</v>
+        <f t="shared" si="5"/>
+        <v>Plover - V - 0004</v>
       </c>
       <c r="K53" t="str">
-        <f>$E53</f>
-        <v>57880169-77673</v>
+        <f t="shared" si="6"/>
+        <v>57880143-61571</v>
       </c>
       <c r="L53" t="str">
-        <f>$F53</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 05</v>
       </c>
       <c r="M53">
-        <f t="shared" si="0"/>
-        <v>37</v>
+        <f t="shared" si="4"/>
+        <v>39</v>
       </c>
       <c r="N53" t="str">
-        <f>$J53&amp;" - "&amp;$L53</f>
-        <v>Whiting - V - 0001 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Plover - V - 0004 - Turf 05</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
@@ -4461,13 +4436,13 @@
         <v>17</v>
       </c>
       <c r="E54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G54">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H54" t="str">
         <f>_xlfn.XLOOKUP($B54,Table24[Misname],Table24[Canonical],$B54)</f>
@@ -4478,75 +4453,75 @@
         <v>43</v>
       </c>
       <c r="J54" t="str">
-        <f>$H54&amp;" - "&amp;$C54&amp;" - "&amp;$D54</f>
+        <f t="shared" si="5"/>
         <v>Whiting - V - 0001</v>
       </c>
       <c r="K54" t="str">
-        <f>$E54</f>
-        <v>57880171-37532</v>
+        <f t="shared" si="6"/>
+        <v>57880169-77673</v>
       </c>
       <c r="L54" t="str">
-        <f>$F54</f>
-        <v>Turf 02</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M54">
-        <f t="shared" si="0"/>
-        <v>34</v>
+        <f t="shared" si="4"/>
+        <v>37</v>
       </c>
       <c r="N54" t="str">
-        <f>$J54&amp;" - "&amp;$L54</f>
-        <v>Whiting - V - 0001 - Turf 02</v>
+        <f t="shared" si="8"/>
+        <v>Whiting - V - 0001 - Turf 01</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E55" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G55">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H55" t="str">
         <f>_xlfn.XLOOKUP($B55,Table24[Misname],Table24[Canonical],$B55)</f>
-        <v>Hull</v>
+        <v>Whiting</v>
       </c>
       <c r="I55">
         <f>_xlfn.XLOOKUP($J55,Table4[ward_name],Table4[priority])</f>
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J55" t="str">
-        <f>$H55&amp;" - "&amp;$C55&amp;" - "&amp;$D55</f>
-        <v>Hull - T - 0006</v>
+        <f t="shared" si="5"/>
+        <v>Whiting - V - 0001</v>
       </c>
       <c r="K55" t="str">
-        <f>$E55</f>
-        <v>57880190-76027</v>
+        <f t="shared" si="6"/>
+        <v>57880171-37532</v>
       </c>
       <c r="L55" t="str">
-        <f>$F55</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 02</v>
       </c>
       <c r="M55">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <f t="shared" si="4"/>
+        <v>34</v>
       </c>
       <c r="N55" t="str">
-        <f>$J55&amp;" - "&amp;$L55</f>
-        <v>Hull - T - 0006 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Whiting - V - 0001 - Turf 02</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
@@ -4563,13 +4538,13 @@
         <v>88</v>
       </c>
       <c r="E56" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G56">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H56" t="str">
         <f>_xlfn.XLOOKUP($B56,Table24[Misname],Table24[Canonical],$B56)</f>
@@ -4580,75 +4555,75 @@
         <v>48</v>
       </c>
       <c r="J56" t="str">
-        <f>$H56&amp;" - "&amp;$C56&amp;" - "&amp;$D56</f>
+        <f t="shared" si="5"/>
         <v>Hull - T - 0006</v>
       </c>
       <c r="K56" t="str">
-        <f>$E56</f>
-        <v>57880191-35886</v>
+        <f t="shared" si="6"/>
+        <v>57880190-76027</v>
       </c>
       <c r="L56" t="str">
-        <f>$F56</f>
-        <v>Turf 02</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M56">
-        <f t="shared" si="0"/>
-        <v>50</v>
+        <f t="shared" si="4"/>
+        <v>32</v>
       </c>
       <c r="N56" t="str">
-        <f>$J56&amp;" - "&amp;$L56</f>
-        <v>Hull - T - 0006 - Turf 02</v>
+        <f t="shared" si="8"/>
+        <v>Hull - T - 0006 - Turf 01</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B57" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E57" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G57">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H57" t="str">
         <f>_xlfn.XLOOKUP($B57,Table24[Misname],Table24[Canonical],$B57)</f>
-        <v>Stevens Point</v>
+        <v>Hull</v>
       </c>
       <c r="I57">
         <f>_xlfn.XLOOKUP($J57,Table4[ward_name],Table4[priority])</f>
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J57" t="str">
-        <f>$H57&amp;" - "&amp;$C57&amp;" - "&amp;$D57</f>
-        <v>Stevens Point - C - 0032</v>
+        <f t="shared" si="5"/>
+        <v>Hull - T - 0006</v>
       </c>
       <c r="K57" t="str">
-        <f>$E57</f>
-        <v>57880331-72540</v>
+        <f t="shared" si="6"/>
+        <v>57880191-35886</v>
       </c>
       <c r="L57" t="str">
-        <f>$F57</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 02</v>
       </c>
       <c r="M57">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="N57" t="str">
-        <f>$J57&amp;" - "&amp;$L57</f>
-        <v>Stevens Point - C - 0032 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Hull - T - 0006 - Turf 02</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
@@ -4665,13 +4640,13 @@
         <v>91</v>
       </c>
       <c r="E58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F58" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G58">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H58" t="str">
         <f>_xlfn.XLOOKUP($B58,Table24[Misname],Table24[Canonical],$B58)</f>
@@ -4682,75 +4657,75 @@
         <v>16</v>
       </c>
       <c r="J58" t="str">
-        <f>$H58&amp;" - "&amp;$C58&amp;" - "&amp;$D58</f>
+        <f t="shared" si="5"/>
         <v>Stevens Point - C - 0032</v>
       </c>
       <c r="K58" t="str">
-        <f>$E58</f>
-        <v>57880332-32399</v>
+        <f t="shared" si="6"/>
+        <v>57880331-72540</v>
       </c>
       <c r="L58" t="str">
-        <f>$F58</f>
-        <v>Turf 02</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M58">
-        <f t="shared" si="0"/>
-        <v>29</v>
+        <f t="shared" si="4"/>
+        <v>38</v>
       </c>
       <c r="N58" t="str">
-        <f>$J58&amp;" - "&amp;$L58</f>
-        <v>Stevens Point - C - 0032 - Turf 02</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0032 - Turf 01</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="E59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G59">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H59" t="str">
         <f>_xlfn.XLOOKUP($B59,Table24[Misname],Table24[Canonical],$B59)</f>
-        <v>Plover</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I59">
         <f>_xlfn.XLOOKUP($J59,Table4[ward_name],Table4[priority])</f>
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J59" t="str">
-        <f>$H59&amp;" - "&amp;$C59&amp;" - "&amp;$D59</f>
-        <v>Plover - V - 0001</v>
+        <f t="shared" si="5"/>
+        <v>Stevens Point - C - 0032</v>
       </c>
       <c r="K59" t="str">
-        <f>$E59</f>
-        <v>57880035-17760</v>
+        <f t="shared" si="6"/>
+        <v>57880332-32399</v>
       </c>
       <c r="L59" t="str">
-        <f>$F59</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 02</v>
       </c>
       <c r="M59">
-        <f t="shared" si="0"/>
-        <v>35</v>
+        <f t="shared" si="4"/>
+        <v>29</v>
       </c>
       <c r="N59" t="str">
-        <f>$J59&amp;" - "&amp;$L59</f>
-        <v>Plover - V - 0001 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0032 - Turf 02</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
@@ -4767,13 +4742,13 @@
         <v>17</v>
       </c>
       <c r="E60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F60" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G60">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H60" t="str">
         <f>_xlfn.XLOOKUP($B60,Table24[Misname],Table24[Canonical],$B60)</f>
@@ -4784,24 +4759,24 @@
         <v>30</v>
       </c>
       <c r="J60" t="str">
-        <f>$H60&amp;" - "&amp;$C60&amp;" - "&amp;$D60</f>
+        <f t="shared" si="5"/>
         <v>Plover - V - 0001</v>
       </c>
       <c r="K60" t="str">
-        <f>$E60</f>
-        <v>57880036-99912</v>
+        <f t="shared" si="6"/>
+        <v>57880035-17760</v>
       </c>
       <c r="L60" t="str">
-        <f>$F60</f>
-        <v>Turf 02</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M60">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f t="shared" si="4"/>
+        <v>35</v>
       </c>
       <c r="N60" t="str">
-        <f>$J60&amp;" - "&amp;$L60</f>
-        <v>Plover - V - 0001 - Turf 02</v>
+        <f t="shared" si="8"/>
+        <v>Plover - V - 0001 - Turf 01</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
@@ -4818,13 +4793,13 @@
         <v>17</v>
       </c>
       <c r="E61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F61" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G61">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H61" t="str">
         <f>_xlfn.XLOOKUP($B61,Table24[Misname],Table24[Canonical],$B61)</f>
@@ -4835,24 +4810,24 @@
         <v>30</v>
       </c>
       <c r="J61" t="str">
-        <f>$H61&amp;" - "&amp;$C61&amp;" - "&amp;$D61</f>
+        <f t="shared" si="5"/>
         <v>Plover - V - 0001</v>
       </c>
       <c r="K61" t="str">
-        <f>$E61</f>
-        <v>57880037-77338</v>
+        <f t="shared" si="6"/>
+        <v>57880036-99912</v>
       </c>
       <c r="L61" t="str">
-        <f>$F61</f>
-        <v>Turf 03</v>
+        <f t="shared" si="7"/>
+        <v>Turf 02</v>
       </c>
       <c r="M61">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>39</v>
       </c>
       <c r="N61" t="str">
-        <f>$J61&amp;" - "&amp;$L61</f>
-        <v>Plover - V - 0001 - Turf 03</v>
+        <f t="shared" si="8"/>
+        <v>Plover - V - 0001 - Turf 02</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
@@ -4869,13 +4844,13 @@
         <v>17</v>
       </c>
       <c r="E62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F62" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G62">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H62" t="str">
         <f>_xlfn.XLOOKUP($B62,Table24[Misname],Table24[Canonical],$B62)</f>
@@ -4886,72 +4861,75 @@
         <v>30</v>
       </c>
       <c r="J62" t="str">
-        <f>$H62&amp;" - "&amp;$C62&amp;" - "&amp;$D62</f>
+        <f t="shared" si="5"/>
         <v>Plover - V - 0001</v>
       </c>
       <c r="K62" t="str">
-        <f>$E62</f>
-        <v>57880038-54763</v>
+        <f t="shared" si="6"/>
+        <v>57880037-77338</v>
       </c>
       <c r="L62" t="str">
-        <f>$F62</f>
-        <v>Turf 04</v>
+        <f t="shared" si="7"/>
+        <v>Turf 03</v>
       </c>
       <c r="M62">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f t="shared" si="4"/>
+        <v>30</v>
       </c>
       <c r="N62" t="str">
-        <f>$J62&amp;" - "&amp;$L62</f>
-        <v>Plover - V - 0001 - Turf 04</v>
+        <f t="shared" si="8"/>
+        <v>Plover - V - 0001 - Turf 03</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="C63" t="s">
+        <v>16</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E63" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F63" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G63">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H63" t="str">
         <f>_xlfn.XLOOKUP($B63,Table24[Misname],Table24[Canonical],$B63)</f>
-        <v>Amherst</v>
-      </c>
-      <c r="I63" t="e">
+        <v>Plover</v>
+      </c>
+      <c r="I63">
         <f>_xlfn.XLOOKUP($J63,Table4[ward_name],Table4[priority])</f>
-        <v>#N/A</v>
+        <v>30</v>
       </c>
       <c r="J63" t="str">
-        <f>$H63&amp;" - "&amp;$C63&amp;" - "&amp;$D63</f>
-        <v>Amherst -  - 0002</v>
+        <f t="shared" si="5"/>
+        <v>Plover - V - 0001</v>
       </c>
       <c r="K63" t="str">
-        <f>$E63</f>
-        <v>57880224-84968</v>
+        <f t="shared" si="6"/>
+        <v>57880038-54763</v>
       </c>
       <c r="L63" t="str">
-        <f>$F63</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 04</v>
       </c>
       <c r="M63">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="N63" t="str">
-        <f>$J63&amp;" - "&amp;$L63</f>
-        <v>Amherst -  - 0002 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Plover - V - 0001 - Turf 04</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
@@ -4965,13 +4943,13 @@
         <v>43</v>
       </c>
       <c r="E64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F64" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G64">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H64" t="str">
         <f>_xlfn.XLOOKUP($B64,Table24[Misname],Table24[Canonical],$B64)</f>
@@ -4982,75 +4960,72 @@
         <v>#N/A</v>
       </c>
       <c r="J64" t="str">
-        <f>$H64&amp;" - "&amp;$C64&amp;" - "&amp;$D64</f>
+        <f t="shared" si="5"/>
         <v>Amherst -  - 0002</v>
       </c>
       <c r="K64" t="str">
-        <f>$E64</f>
-        <v>57880225-44827</v>
+        <f t="shared" si="6"/>
+        <v>57880224-84968</v>
       </c>
       <c r="L64" t="str">
-        <f>$F64</f>
-        <v>Turf 02</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M64">
-        <f t="shared" si="0"/>
-        <v>31</v>
+        <f t="shared" si="4"/>
+        <v>38</v>
       </c>
       <c r="N64" t="str">
-        <f>$J64&amp;" - "&amp;$L64</f>
-        <v>Amherst -  - 0002 - Turf 02</v>
+        <f t="shared" si="8"/>
+        <v>Amherst -  - 0002 - Turf 01</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B65" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="E65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F65" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G65">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="H65" t="str">
         <f>_xlfn.XLOOKUP($B65,Table24[Misname],Table24[Canonical],$B65)</f>
-        <v>Stevens Point</v>
-      </c>
-      <c r="I65">
+        <v>Amherst</v>
+      </c>
+      <c r="I65" t="e">
         <f>_xlfn.XLOOKUP($J65,Table4[ward_name],Table4[priority])</f>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
       <c r="J65" t="str">
-        <f>$H65&amp;" - "&amp;$C65&amp;" - "&amp;$D65</f>
-        <v>Stevens Point - C - 0008</v>
+        <f t="shared" si="5"/>
+        <v>Amherst -  - 0002</v>
       </c>
       <c r="K65" t="str">
-        <f>$E65</f>
-        <v>57880023-72818</v>
+        <f t="shared" si="6"/>
+        <v>57880225-44827</v>
       </c>
       <c r="L65" t="str">
-        <f>$F65</f>
-        <v>Turf 01</v>
+        <f t="shared" si="7"/>
+        <v>Turf 02</v>
       </c>
       <c r="M65">
-        <f t="shared" si="0"/>
-        <v>51</v>
+        <f t="shared" si="4"/>
+        <v>31</v>
       </c>
       <c r="N65" t="str">
-        <f>$J65&amp;" - "&amp;$L65</f>
-        <v>Stevens Point - C - 0008 - Turf 01</v>
+        <f t="shared" si="8"/>
+        <v>Amherst -  - 0002 - Turf 02</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
@@ -5067,13 +5042,13 @@
         <v>78</v>
       </c>
       <c r="E66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F66" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G66">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H66" t="str">
         <f>_xlfn.XLOOKUP($B66,Table24[Misname],Table24[Canonical],$B66)</f>
@@ -5084,75 +5059,75 @@
         <v>1</v>
       </c>
       <c r="J66" t="str">
-        <f>$H66&amp;" - "&amp;$C66&amp;" - "&amp;$D66</f>
+        <f t="shared" si="5"/>
         <v>Stevens Point - C - 0008</v>
       </c>
       <c r="K66" t="str">
-        <f>$E66</f>
-        <v>57880024-32677</v>
+        <f t="shared" si="6"/>
+        <v>57880023-72818</v>
       </c>
       <c r="L66" t="str">
-        <f>$F66</f>
-        <v>Turf 02</v>
+        <f t="shared" si="7"/>
+        <v>Turf 01</v>
       </c>
       <c r="M66">
-        <f t="shared" si="0"/>
-        <v>56</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="N66" t="str">
-        <f>$J66&amp;" - "&amp;$L66</f>
-        <v>Stevens Point - C - 0008 - Turf 02</v>
+        <f t="shared" si="8"/>
+        <v>Stevens Point - C - 0008 - Turf 01</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B67" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F67" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G67">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H67" t="str">
         <f>_xlfn.XLOOKUP($B67,Table24[Misname],Table24[Canonical],$B67)</f>
-        <v>Plover</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I67">
         <f>_xlfn.XLOOKUP($J67,Table4[ward_name],Table4[priority])</f>
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="J67" t="str">
-        <f>$H67&amp;" - "&amp;$C67&amp;" - "&amp;$D67</f>
-        <v>Plover - V - 0010</v>
+        <f t="shared" ref="J67:J98" si="9">$H67&amp;" - "&amp;$C67&amp;" - "&amp;$D67</f>
+        <v>Stevens Point - C - 0008</v>
       </c>
       <c r="K67" t="str">
-        <f>$E67</f>
-        <v>57880265-12372</v>
+        <f t="shared" ref="K67:K98" si="10">$E67</f>
+        <v>57880024-32677</v>
       </c>
       <c r="L67" t="str">
-        <f>$F67</f>
-        <v>Turf 01</v>
+        <f t="shared" ref="L67:L98" si="11">$F67</f>
+        <v>Turf 02</v>
       </c>
       <c r="M67">
-        <f t="shared" ref="M67:M130" si="1">$G67</f>
-        <v>45</v>
+        <f t="shared" si="4"/>
+        <v>56</v>
       </c>
       <c r="N67" t="str">
-        <f>$J67&amp;" - "&amp;$L67</f>
-        <v>Plover - V - 0010 - Turf 01</v>
+        <f t="shared" ref="N67:N98" si="12">$J67&amp;" - "&amp;$L67</f>
+        <v>Stevens Point - C - 0008 - Turf 02</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
@@ -5169,13 +5144,13 @@
         <v>71</v>
       </c>
       <c r="E68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F68" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G68">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H68" t="str">
         <f>_xlfn.XLOOKUP($B68,Table24[Misname],Table24[Canonical],$B68)</f>
@@ -5186,24 +5161,24 @@
         <v>33</v>
       </c>
       <c r="J68" t="str">
-        <f>$H68&amp;" - "&amp;$C68&amp;" - "&amp;$D68</f>
+        <f t="shared" si="9"/>
         <v>Plover - V - 0010</v>
       </c>
       <c r="K68" t="str">
-        <f>$E68</f>
-        <v>57880266-29938</v>
+        <f t="shared" si="10"/>
+        <v>57880265-12372</v>
       </c>
       <c r="L68" t="str">
-        <f>$F68</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M68">
-        <f t="shared" si="1"/>
-        <v>44</v>
+        <f t="shared" ref="M68:M131" si="13">$G68</f>
+        <v>45</v>
       </c>
       <c r="N68" t="str">
-        <f>$J68&amp;" - "&amp;$L68</f>
-        <v>Plover - V - 0010 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0010 - Turf 01</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
@@ -5220,13 +5195,13 @@
         <v>71</v>
       </c>
       <c r="E69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F69" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G69">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H69" t="str">
         <f>_xlfn.XLOOKUP($B69,Table24[Misname],Table24[Canonical],$B69)</f>
@@ -5237,29 +5212,29 @@
         <v>33</v>
       </c>
       <c r="J69" t="str">
-        <f>$H69&amp;" - "&amp;$C69&amp;" - "&amp;$D69</f>
+        <f t="shared" si="9"/>
         <v>Plover - V - 0010</v>
       </c>
       <c r="K69" t="str">
-        <f>$E69</f>
-        <v>57880267-47505</v>
+        <f t="shared" si="10"/>
+        <v>57880266-29938</v>
       </c>
       <c r="L69" t="str">
-        <f>$F69</f>
-        <v>Turf 03</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M69">
-        <f t="shared" si="1"/>
-        <v>27</v>
+        <f t="shared" si="13"/>
+        <v>44</v>
       </c>
       <c r="N69" t="str">
-        <f>$J69&amp;" - "&amp;$L69</f>
-        <v>Plover - V - 0010 - Turf 03</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0010 - Turf 02</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B70" t="s">
         <v>22</v>
@@ -5268,16 +5243,16 @@
         <v>16</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="E70" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F70" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G70">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="H70" t="str">
         <f>_xlfn.XLOOKUP($B70,Table24[Misname],Table24[Canonical],$B70)</f>
@@ -5285,27 +5260,27 @@
       </c>
       <c r="I70">
         <f>_xlfn.XLOOKUP($J70,Table4[ward_name],Table4[priority])</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J70" t="str">
-        <f>$H70&amp;" - "&amp;$C70&amp;" - "&amp;$D70</f>
-        <v>Plover - V - 0003</v>
+        <f t="shared" si="9"/>
+        <v>Plover - V - 0010</v>
       </c>
       <c r="K70" t="str">
-        <f>$E70</f>
-        <v>57880087-57638</v>
+        <f t="shared" si="10"/>
+        <v>57880267-47505</v>
       </c>
       <c r="L70" t="str">
-        <f>$F70</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 03</v>
       </c>
       <c r="M70">
-        <f t="shared" si="1"/>
-        <v>52</v>
+        <f t="shared" si="13"/>
+        <v>27</v>
       </c>
       <c r="N70" t="str">
-        <f>$J70&amp;" - "&amp;$L70</f>
-        <v>Plover - V - 0003 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0010 - Turf 03</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
@@ -5322,13 +5297,13 @@
         <v>106</v>
       </c>
       <c r="E71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G71">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H71" t="str">
         <f>_xlfn.XLOOKUP($B71,Table24[Misname],Table24[Canonical],$B71)</f>
@@ -5339,24 +5314,24 @@
         <v>34</v>
       </c>
       <c r="J71" t="str">
-        <f>$H71&amp;" - "&amp;$C71&amp;" - "&amp;$D71</f>
+        <f t="shared" si="9"/>
         <v>Plover - V - 0003</v>
       </c>
       <c r="K71" t="str">
-        <f>$E71</f>
-        <v>57880088-17497</v>
+        <f t="shared" si="10"/>
+        <v>57880087-57638</v>
       </c>
       <c r="L71" t="str">
-        <f>$F71</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M71">
-        <f t="shared" si="1"/>
-        <v>45</v>
+        <f t="shared" si="13"/>
+        <v>52</v>
       </c>
       <c r="N71" t="str">
-        <f>$J71&amp;" - "&amp;$L71</f>
-        <v>Plover - V - 0003 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0003 - Turf 01</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
@@ -5373,10 +5348,10 @@
         <v>106</v>
       </c>
       <c r="E72" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F72" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G72">
         <v>45</v>
@@ -5390,75 +5365,75 @@
         <v>34</v>
       </c>
       <c r="J72" t="str">
-        <f>$H72&amp;" - "&amp;$C72&amp;" - "&amp;$D72</f>
+        <f t="shared" si="9"/>
         <v>Plover - V - 0003</v>
       </c>
       <c r="K72" t="str">
-        <f>$E72</f>
-        <v>57880089-99649</v>
+        <f t="shared" si="10"/>
+        <v>57880088-17497</v>
       </c>
       <c r="L72" t="str">
-        <f>$F72</f>
-        <v>Turf 03</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>45</v>
       </c>
       <c r="N72" t="str">
-        <f>$J72&amp;" - "&amp;$L72</f>
-        <v>Plover - V - 0003 - Turf 03</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0003 - Turf 02</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B73" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="E73" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F73" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G73">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H73" t="str">
         <f>_xlfn.XLOOKUP($B73,Table24[Misname],Table24[Canonical],$B73)</f>
-        <v>Stevens Point</v>
+        <v>Plover</v>
       </c>
       <c r="I73">
         <f>_xlfn.XLOOKUP($J73,Table4[ward_name],Table4[priority])</f>
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="J73" t="str">
-        <f>$H73&amp;" - "&amp;$C73&amp;" - "&amp;$D73</f>
-        <v>Stevens Point - C - 0004</v>
+        <f t="shared" si="9"/>
+        <v>Plover - V - 0003</v>
       </c>
       <c r="K73" t="str">
-        <f>$E73</f>
-        <v>57880096-51065</v>
+        <f t="shared" si="10"/>
+        <v>57880089-99649</v>
       </c>
       <c r="L73" t="str">
-        <f>$F73</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 03</v>
       </c>
       <c r="M73">
-        <f t="shared" si="1"/>
-        <v>57</v>
+        <f t="shared" si="13"/>
+        <v>45</v>
       </c>
       <c r="N73" t="str">
-        <f>$J73&amp;" - "&amp;$L73</f>
-        <v>Stevens Point - C - 0004 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0003 - Turf 03</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
@@ -5475,13 +5450,13 @@
         <v>80</v>
       </c>
       <c r="E74" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F74" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G74">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="H74" t="str">
         <f>_xlfn.XLOOKUP($B74,Table24[Misname],Table24[Canonical],$B74)</f>
@@ -5492,24 +5467,24 @@
         <v>9</v>
       </c>
       <c r="J74" t="str">
-        <f>$H74&amp;" - "&amp;$C74&amp;" - "&amp;$D74</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point - C - 0004</v>
       </c>
       <c r="K74" t="str">
-        <f>$E74</f>
-        <v>57880097-10924</v>
+        <f t="shared" si="10"/>
+        <v>57880096-51065</v>
       </c>
       <c r="L74" t="str">
-        <f>$F74</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M74">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f t="shared" si="13"/>
+        <v>57</v>
       </c>
       <c r="N74" t="str">
-        <f>$J74&amp;" - "&amp;$L74</f>
-        <v>Stevens Point - C - 0004 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0004 - Turf 01</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
@@ -5526,13 +5501,13 @@
         <v>80</v>
       </c>
       <c r="E75" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F75" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G75">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H75" t="str">
         <f>_xlfn.XLOOKUP($B75,Table24[Misname],Table24[Canonical],$B75)</f>
@@ -5543,24 +5518,24 @@
         <v>9</v>
       </c>
       <c r="J75" t="str">
-        <f>$H75&amp;" - "&amp;$C75&amp;" - "&amp;$D75</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point - C - 0004</v>
       </c>
       <c r="K75" t="str">
-        <f>$E75</f>
-        <v>57880098-28491</v>
+        <f t="shared" si="10"/>
+        <v>57880097-10924</v>
       </c>
       <c r="L75" t="str">
-        <f>$F75</f>
-        <v>Turf 03</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M75">
-        <f t="shared" si="1"/>
-        <v>38</v>
+        <f t="shared" si="13"/>
+        <v>42</v>
       </c>
       <c r="N75" t="str">
-        <f>$J75&amp;" - "&amp;$L75</f>
-        <v>Stevens Point - C - 0004 - Turf 03</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0004 - Turf 02</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
@@ -5577,13 +5552,13 @@
         <v>80</v>
       </c>
       <c r="E76" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F76" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G76">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H76" t="str">
         <f>_xlfn.XLOOKUP($B76,Table24[Misname],Table24[Canonical],$B76)</f>
@@ -5594,29 +5569,29 @@
         <v>9</v>
       </c>
       <c r="J76" t="str">
-        <f>$H76&amp;" - "&amp;$C76&amp;" - "&amp;$D76</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point - C - 0004</v>
       </c>
       <c r="K76" t="str">
-        <f>$E76</f>
-        <v>57880099-78350</v>
+        <f t="shared" si="10"/>
+        <v>57880098-28491</v>
       </c>
       <c r="L76" t="str">
-        <f>$F76</f>
-        <v>Turf 04</v>
+        <f t="shared" si="11"/>
+        <v>Turf 03</v>
       </c>
       <c r="M76">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f t="shared" si="13"/>
+        <v>38</v>
       </c>
       <c r="N76" t="str">
-        <f>$J76&amp;" - "&amp;$L76</f>
-        <v>Stevens Point - C - 0004 - Turf 04</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0004 - Turf 03</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B77" t="s">
         <v>6</v>
@@ -5625,16 +5600,16 @@
         <v>7</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E77" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F77" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G77">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H77" t="str">
         <f>_xlfn.XLOOKUP($B77,Table24[Misname],Table24[Canonical],$B77)</f>
@@ -5642,27 +5617,27 @@
       </c>
       <c r="I77">
         <f>_xlfn.XLOOKUP($J77,Table4[ward_name],Table4[priority])</f>
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J77" t="str">
-        <f>$H77&amp;" - "&amp;$C77&amp;" - "&amp;$D77</f>
-        <v>Stevens Point - C - 0019</v>
+        <f t="shared" si="9"/>
+        <v>Stevens Point - C - 0004</v>
       </c>
       <c r="K77" t="str">
-        <f>$E77</f>
-        <v>57880154-42838</v>
+        <f t="shared" si="10"/>
+        <v>57880099-78350</v>
       </c>
       <c r="L77" t="str">
-        <f>$F77</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 04</v>
       </c>
       <c r="M77">
-        <f t="shared" si="1"/>
-        <v>44</v>
+        <f t="shared" si="13"/>
+        <v>40</v>
       </c>
       <c r="N77" t="str">
-        <f>$J77&amp;" - "&amp;$L77</f>
-        <v>Stevens Point - C - 0019 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0004 - Turf 04</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
@@ -5679,13 +5654,13 @@
         <v>114</v>
       </c>
       <c r="E78" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F78" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G78">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H78" t="str">
         <f>_xlfn.XLOOKUP($B78,Table24[Misname],Table24[Canonical],$B78)</f>
@@ -5696,29 +5671,29 @@
         <v>24</v>
       </c>
       <c r="J78" t="str">
-        <f>$H78&amp;" - "&amp;$C78&amp;" - "&amp;$D78</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point - C - 0019</v>
       </c>
       <c r="K78" t="str">
-        <f>$E78</f>
-        <v>57880155-92697</v>
+        <f t="shared" si="10"/>
+        <v>57880154-42838</v>
       </c>
       <c r="L78" t="str">
-        <f>$F78</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M78">
-        <f t="shared" si="1"/>
-        <v>45</v>
+        <f t="shared" si="13"/>
+        <v>44</v>
       </c>
       <c r="N78" t="str">
-        <f>$J78&amp;" - "&amp;$L78</f>
-        <v>Stevens Point - C - 0019 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0019 - Turf 01</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B79" t="s">
         <v>6</v>
@@ -5727,16 +5702,16 @@
         <v>7</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F79" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G79">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H79" t="str">
         <f>_xlfn.XLOOKUP($B79,Table24[Misname],Table24[Canonical],$B79)</f>
@@ -5744,50 +5719,50 @@
       </c>
       <c r="I79">
         <f>_xlfn.XLOOKUP($J79,Table4[ward_name],Table4[priority])</f>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J79" t="str">
-        <f>$H79&amp;" - "&amp;$C79&amp;" - "&amp;$D79</f>
-        <v>Stevens Point - C - 0029</v>
+        <f t="shared" si="9"/>
+        <v>Stevens Point - C - 0019</v>
       </c>
       <c r="K79" t="str">
-        <f>$E79</f>
-        <v>57880326-92275</v>
+        <f t="shared" si="10"/>
+        <v>57880155-92697</v>
       </c>
       <c r="L79" t="str">
-        <f>$F79</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M79">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f t="shared" si="13"/>
+        <v>45</v>
       </c>
       <c r="N79" t="str">
-        <f>$J79&amp;" - "&amp;$L79</f>
-        <v>Stevens Point - C - 0029 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0019 - Turf 02</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C80" t="s">
         <v>7</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E80" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F80" t="s">
         <v>10</v>
       </c>
       <c r="G80">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H80" t="str">
         <f>_xlfn.XLOOKUP($B80,Table24[Misname],Table24[Canonical],$B80)</f>
@@ -5795,27 +5770,27 @@
       </c>
       <c r="I80">
         <f>_xlfn.XLOOKUP($J80,Table4[ward_name],Table4[priority])</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J80" t="str">
-        <f>$H80&amp;" - "&amp;$C80&amp;" - "&amp;$D80</f>
-        <v>Stevens Point - C - 0025</v>
+        <f t="shared" si="9"/>
+        <v>Stevens Point - C - 0029</v>
       </c>
       <c r="K80" t="str">
-        <f>$E80</f>
-        <v>57880307-51439</v>
+        <f t="shared" si="10"/>
+        <v>57880326-92275</v>
       </c>
       <c r="L80" t="str">
-        <f>$F80</f>
+        <f t="shared" si="11"/>
         <v>Turf 01</v>
       </c>
       <c r="M80">
-        <f t="shared" si="1"/>
-        <v>34</v>
+        <f t="shared" si="13"/>
+        <v>35</v>
       </c>
       <c r="N80" t="str">
-        <f>$J80&amp;" - "&amp;$L80</f>
-        <v>Stevens Point - C - 0025 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0029 - Turf 01</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
@@ -5832,13 +5807,13 @@
         <v>119</v>
       </c>
       <c r="E81" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F81" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G81">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H81" t="str">
         <f>_xlfn.XLOOKUP($B81,Table24[Misname],Table24[Canonical],$B81)</f>
@@ -5849,29 +5824,29 @@
         <v>8</v>
       </c>
       <c r="J81" t="str">
-        <f>$H81&amp;" - "&amp;$C81&amp;" - "&amp;$D81</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point - C - 0025</v>
       </c>
       <c r="K81" t="str">
-        <f>$E81</f>
-        <v>57880308-93449</v>
+        <f t="shared" si="10"/>
+        <v>57880307-51439</v>
       </c>
       <c r="L81" t="str">
-        <f>$F81</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M81">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f t="shared" si="13"/>
+        <v>34</v>
       </c>
       <c r="N81" t="str">
-        <f>$J81&amp;" - "&amp;$L81</f>
-        <v>Stevens Point - C - 0025 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0025 - Turf 01</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B82" t="s">
         <v>47</v>
@@ -5880,16 +5855,16 @@
         <v>7</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="E82" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F82" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G82">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H82" t="str">
         <f>_xlfn.XLOOKUP($B82,Table24[Misname],Table24[Canonical],$B82)</f>
@@ -5897,27 +5872,27 @@
       </c>
       <c r="I82">
         <f>_xlfn.XLOOKUP($J82,Table4[ward_name],Table4[priority])</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J82" t="str">
-        <f>$H82&amp;" - "&amp;$C82&amp;" - "&amp;$D82</f>
-        <v>Stevens Point - C - 0002</v>
+        <f t="shared" si="9"/>
+        <v>Stevens Point - C - 0025</v>
       </c>
       <c r="K82" t="str">
-        <f>$E82</f>
-        <v>57880273-16966</v>
+        <f t="shared" si="10"/>
+        <v>57880308-93449</v>
       </c>
       <c r="L82" t="str">
-        <f>$F82</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M82">
-        <f t="shared" si="1"/>
-        <v>36</v>
+        <f t="shared" si="13"/>
+        <v>35</v>
       </c>
       <c r="N82" t="str">
-        <f>$J82&amp;" - "&amp;$L82</f>
-        <v>Stevens Point - C - 0002 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0025 - Turf 02</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
@@ -5934,13 +5909,13 @@
         <v>43</v>
       </c>
       <c r="E83" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F83" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G83">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H83" t="str">
         <f>_xlfn.XLOOKUP($B83,Table24[Misname],Table24[Canonical],$B83)</f>
@@ -5951,24 +5926,24 @@
         <v>6</v>
       </c>
       <c r="J83" t="str">
-        <f>$H83&amp;" - "&amp;$C83&amp;" - "&amp;$D83</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point - C - 0002</v>
       </c>
       <c r="K83" t="str">
-        <f>$E83</f>
-        <v>57880274-34533</v>
+        <f t="shared" si="10"/>
+        <v>57880273-16966</v>
       </c>
       <c r="L83" t="str">
-        <f>$F83</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M83">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f t="shared" si="13"/>
+        <v>36</v>
       </c>
       <c r="N83" t="str">
-        <f>$J83&amp;" - "&amp;$L83</f>
-        <v>Stevens Point - C - 0002 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0002 - Turf 01</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
@@ -5985,13 +5960,13 @@
         <v>43</v>
       </c>
       <c r="E84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F84" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G84">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H84" t="str">
         <f>_xlfn.XLOOKUP($B84,Table24[Misname],Table24[Canonical],$B84)</f>
@@ -6002,72 +5977,75 @@
         <v>6</v>
       </c>
       <c r="J84" t="str">
-        <f>$H84&amp;" - "&amp;$C84&amp;" - "&amp;$D84</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point - C - 0002</v>
       </c>
       <c r="K84" t="str">
-        <f>$E84</f>
-        <v>57880275-84392</v>
+        <f t="shared" si="10"/>
+        <v>57880274-34533</v>
       </c>
       <c r="L84" t="str">
-        <f>$F84</f>
-        <v>Turf 03</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M84">
-        <f t="shared" si="1"/>
-        <v>37</v>
+        <f t="shared" si="13"/>
+        <v>42</v>
       </c>
       <c r="N84" t="str">
-        <f>$J84&amp;" - "&amp;$L84</f>
-        <v>Stevens Point - C - 0002 - Turf 03</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0002 - Turf 02</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B85" t="s">
-        <v>6</v>
+        <v>47</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="E85" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F85" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G85">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H85" t="str">
         <f>_xlfn.XLOOKUP($B85,Table24[Misname],Table24[Canonical],$B85)</f>
         <v>Stevens Point</v>
       </c>
-      <c r="I85" t="e">
+      <c r="I85">
         <f>_xlfn.XLOOKUP($J85,Table4[ward_name],Table4[priority])</f>
-        <v>#N/A</v>
+        <v>6</v>
       </c>
       <c r="J85" t="str">
-        <f>$H85&amp;" - "&amp;$C85&amp;" - "&amp;$D85</f>
-        <v>Stevens Point -  - 0033</v>
+        <f t="shared" si="9"/>
+        <v>Stevens Point - C - 0002</v>
       </c>
       <c r="K85" t="str">
-        <f>$E85</f>
-        <v>57880156-33916</v>
+        <f t="shared" si="10"/>
+        <v>57880275-84392</v>
       </c>
       <c r="L85" t="str">
-        <f>$F85</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 03</v>
       </c>
       <c r="M85">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f t="shared" si="13"/>
+        <v>37</v>
       </c>
       <c r="N85" t="str">
-        <f>$J85&amp;" - "&amp;$L85</f>
-        <v>Stevens Point -  - 0033 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0002 - Turf 03</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
@@ -6081,13 +6059,13 @@
         <v>125</v>
       </c>
       <c r="E86" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F86" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G86">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H86" t="str">
         <f>_xlfn.XLOOKUP($B86,Table24[Misname],Table24[Canonical],$B86)</f>
@@ -6098,80 +6076,77 @@
         <v>#N/A</v>
       </c>
       <c r="J86" t="str">
-        <f>$H86&amp;" - "&amp;$C86&amp;" - "&amp;$D86</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point -  - 0033</v>
       </c>
       <c r="K86" t="str">
-        <f>$E86</f>
-        <v>57880157-83775</v>
+        <f t="shared" si="10"/>
+        <v>57880156-33916</v>
       </c>
       <c r="L86" t="str">
-        <f>$F86</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M86">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="13"/>
+        <v>35</v>
       </c>
       <c r="N86" t="str">
-        <f>$J86&amp;" - "&amp;$L86</f>
-        <v>Stevens Point -  - 0033 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point -  - 0033 - Turf 01</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B87" t="s">
         <v>6</v>
       </c>
-      <c r="C87" t="s">
-        <v>7</v>
-      </c>
       <c r="D87" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E87" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F87" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G87">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H87" t="str">
         <f>_xlfn.XLOOKUP($B87,Table24[Misname],Table24[Canonical],$B87)</f>
         <v>Stevens Point</v>
       </c>
-      <c r="I87">
+      <c r="I87" t="e">
         <f>_xlfn.XLOOKUP($J87,Table4[ward_name],Table4[priority])</f>
-        <v>13</v>
+        <v>#N/A</v>
       </c>
       <c r="J87" t="str">
-        <f>$H87&amp;" - "&amp;$C87&amp;" - "&amp;$D87</f>
-        <v>Stevens Point - C - 0021</v>
+        <f t="shared" si="9"/>
+        <v>Stevens Point -  - 0033</v>
       </c>
       <c r="K87" t="str">
-        <f>$E87</f>
-        <v>57880319-46828</v>
+        <f t="shared" si="10"/>
+        <v>57880157-83775</v>
       </c>
       <c r="L87" t="str">
-        <f>$F87</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M87">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="13"/>
+        <v>50</v>
       </c>
       <c r="N87" t="str">
-        <f>$J87&amp;" - "&amp;$L87</f>
-        <v>Stevens Point - C - 0021 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point -  - 0033 - Turf 02</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B88" t="s">
         <v>6</v>
@@ -6180,16 +6155,16 @@
         <v>7</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E88" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F88" t="s">
         <v>10</v>
       </c>
       <c r="G88">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H88" t="str">
         <f>_xlfn.XLOOKUP($B88,Table24[Misname],Table24[Canonical],$B88)</f>
@@ -6197,27 +6172,27 @@
       </c>
       <c r="I88">
         <f>_xlfn.XLOOKUP($J88,Table4[ward_name],Table4[priority])</f>
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J88" t="str">
-        <f>$H88&amp;" - "&amp;$C88&amp;" - "&amp;$D88</f>
-        <v>Stevens Point - C - 0022</v>
+        <f t="shared" si="9"/>
+        <v>Stevens Point - C - 0021</v>
       </c>
       <c r="K88" t="str">
-        <f>$E88</f>
-        <v>57880323-69808</v>
+        <f t="shared" si="10"/>
+        <v>57880319-46828</v>
       </c>
       <c r="L88" t="str">
-        <f>$F88</f>
+        <f t="shared" si="11"/>
         <v>Turf 01</v>
       </c>
       <c r="M88">
-        <f t="shared" si="1"/>
-        <v>58</v>
+        <f t="shared" si="13"/>
+        <v>53</v>
       </c>
       <c r="N88" t="str">
-        <f>$J88&amp;" - "&amp;$L88</f>
-        <v>Stevens Point - C - 0022 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0021 - Turf 01</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
@@ -6234,13 +6209,13 @@
         <v>130</v>
       </c>
       <c r="E89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F89" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G89">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H89" t="str">
         <f>_xlfn.XLOOKUP($B89,Table24[Misname],Table24[Canonical],$B89)</f>
@@ -6251,24 +6226,24 @@
         <v>19</v>
       </c>
       <c r="J89" t="str">
-        <f>$H89&amp;" - "&amp;$C89&amp;" - "&amp;$D89</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point - C - 0022</v>
       </c>
       <c r="K89" t="str">
-        <f>$E89</f>
-        <v>57880324-87375</v>
+        <f t="shared" si="10"/>
+        <v>57880323-69808</v>
       </c>
       <c r="L89" t="str">
-        <f>$F89</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M89">
-        <f t="shared" si="1"/>
-        <v>52</v>
+        <f t="shared" si="13"/>
+        <v>58</v>
       </c>
       <c r="N89" t="str">
-        <f>$J89&amp;" - "&amp;$L89</f>
-        <v>Stevens Point - C - 0022 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0022 - Turf 01</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
@@ -6285,13 +6260,13 @@
         <v>130</v>
       </c>
       <c r="E90" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F90" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G90">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H90" t="str">
         <f>_xlfn.XLOOKUP($B90,Table24[Misname],Table24[Canonical],$B90)</f>
@@ -6302,75 +6277,75 @@
         <v>19</v>
       </c>
       <c r="J90" t="str">
-        <f>$H90&amp;" - "&amp;$C90&amp;" - "&amp;$D90</f>
+        <f t="shared" si="9"/>
         <v>Stevens Point - C - 0022</v>
       </c>
       <c r="K90" t="str">
-        <f>$E90</f>
-        <v>57880325-14941</v>
+        <f t="shared" si="10"/>
+        <v>57880324-87375</v>
       </c>
       <c r="L90" t="str">
-        <f>$F90</f>
-        <v>Turf 03</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M90">
-        <f t="shared" si="1"/>
-        <v>43</v>
+        <f t="shared" si="13"/>
+        <v>52</v>
       </c>
       <c r="N90" t="str">
-        <f>$J90&amp;" - "&amp;$L90</f>
-        <v>Stevens Point - C - 0022 - Turf 03</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0022 - Turf 02</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B91" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="C91" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="E91" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F91" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G91">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="H91" t="str">
         <f>_xlfn.XLOOKUP($B91,Table24[Misname],Table24[Canonical],$B91)</f>
-        <v>Hull</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I91">
         <f>_xlfn.XLOOKUP($J91,Table4[ward_name],Table4[priority])</f>
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="J91" t="str">
-        <f>$H91&amp;" - "&amp;$C91&amp;" - "&amp;$D91</f>
-        <v>Hull - T - 0004</v>
+        <f t="shared" si="9"/>
+        <v>Stevens Point - C - 0022</v>
       </c>
       <c r="K91" t="str">
-        <f>$E91</f>
-        <v>57880059-17571</v>
+        <f t="shared" si="10"/>
+        <v>57880325-14941</v>
       </c>
       <c r="L91" t="str">
-        <f>$F91</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 03</v>
       </c>
       <c r="M91">
-        <f t="shared" si="1"/>
-        <v>60</v>
+        <f t="shared" si="13"/>
+        <v>43</v>
       </c>
       <c r="N91" t="str">
-        <f>$J91&amp;" - "&amp;$L91</f>
-        <v>Hull - T - 0004 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Stevens Point - C - 0022 - Turf 03</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
@@ -6387,13 +6362,13 @@
         <v>80</v>
       </c>
       <c r="E92" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F92" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G92">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H92" t="str">
         <f>_xlfn.XLOOKUP($B92,Table24[Misname],Table24[Canonical],$B92)</f>
@@ -6404,75 +6379,75 @@
         <v>49</v>
       </c>
       <c r="J92" t="str">
-        <f>$H92&amp;" - "&amp;$C92&amp;" - "&amp;$D92</f>
+        <f t="shared" si="9"/>
         <v>Hull - T - 0004</v>
       </c>
       <c r="K92" t="str">
-        <f>$E92</f>
-        <v>57880060-67430</v>
+        <f t="shared" si="10"/>
+        <v>57880059-17571</v>
       </c>
       <c r="L92" t="str">
-        <f>$F92</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M92">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="13"/>
+        <v>60</v>
       </c>
       <c r="N92" t="str">
-        <f>$J92&amp;" - "&amp;$L92</f>
-        <v>Hull - T - 0004 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Hull - T - 0004 - Turf 01</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E93" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F93" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G93">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="H93" t="str">
         <f>_xlfn.XLOOKUP($B93,Table24[Misname],Table24[Canonical],$B93)</f>
-        <v>Plover</v>
+        <v>Hull</v>
       </c>
       <c r="I93">
         <f>_xlfn.XLOOKUP($J93,Table4[ward_name],Table4[priority])</f>
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="J93" t="str">
-        <f>$H93&amp;" - "&amp;$C93&amp;" - "&amp;$D93</f>
-        <v>Plover - V - 0006</v>
+        <f t="shared" si="9"/>
+        <v>Hull - T - 0004</v>
       </c>
       <c r="K93" t="str">
-        <f>$E93</f>
-        <v>57880226-94489</v>
+        <f t="shared" si="10"/>
+        <v>57880060-67430</v>
       </c>
       <c r="L93" t="str">
-        <f>$F93</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M93">
-        <f t="shared" si="1"/>
-        <v>38</v>
+        <f t="shared" si="13"/>
+        <v>53</v>
       </c>
       <c r="N93" t="str">
-        <f>$J93&amp;" - "&amp;$L93</f>
-        <v>Plover - V - 0006 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Hull - T - 0004 - Turf 02</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
@@ -6489,13 +6464,13 @@
         <v>88</v>
       </c>
       <c r="E94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F94" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G94">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H94" t="str">
         <f>_xlfn.XLOOKUP($B94,Table24[Misname],Table24[Canonical],$B94)</f>
@@ -6506,24 +6481,24 @@
         <v>41</v>
       </c>
       <c r="J94" t="str">
-        <f>$H94&amp;" - "&amp;$C94&amp;" - "&amp;$D94</f>
+        <f t="shared" si="9"/>
         <v>Plover - V - 0006</v>
       </c>
       <c r="K94" t="str">
-        <f>$E94</f>
-        <v>57880227-54348</v>
+        <f t="shared" si="10"/>
+        <v>57880226-94489</v>
       </c>
       <c r="L94" t="str">
-        <f>$F94</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M94">
-        <f t="shared" si="1"/>
-        <v>31</v>
+        <f t="shared" si="13"/>
+        <v>38</v>
       </c>
       <c r="N94" t="str">
-        <f>$J94&amp;" - "&amp;$L94</f>
-        <v>Plover - V - 0006 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0006 - Turf 01</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
@@ -6540,13 +6515,13 @@
         <v>88</v>
       </c>
       <c r="E95" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F95" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G95">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="H95" t="str">
         <f>_xlfn.XLOOKUP($B95,Table24[Misname],Table24[Canonical],$B95)</f>
@@ -6557,24 +6532,24 @@
         <v>41</v>
       </c>
       <c r="J95" t="str">
-        <f>$H95&amp;" - "&amp;$C95&amp;" - "&amp;$D95</f>
+        <f t="shared" si="9"/>
         <v>Plover - V - 0006</v>
       </c>
       <c r="K95" t="str">
-        <f>$E95</f>
-        <v>57880228-71915</v>
+        <f t="shared" si="10"/>
+        <v>57880227-54348</v>
       </c>
       <c r="L95" t="str">
-        <f>$F95</f>
-        <v>Turf 03</v>
+        <f t="shared" si="11"/>
+        <v>Turf 02</v>
       </c>
       <c r="M95">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="13"/>
+        <v>31</v>
       </c>
       <c r="N95" t="str">
-        <f>$J95&amp;" - "&amp;$L95</f>
-        <v>Plover - V - 0006 - Turf 03</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0006 - Turf 02</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
@@ -6591,13 +6566,13 @@
         <v>88</v>
       </c>
       <c r="E96" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F96" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G96">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H96" t="str">
         <f>_xlfn.XLOOKUP($B96,Table24[Misname],Table24[Canonical],$B96)</f>
@@ -6608,29 +6583,29 @@
         <v>41</v>
       </c>
       <c r="J96" t="str">
-        <f>$H96&amp;" - "&amp;$C96&amp;" - "&amp;$D96</f>
+        <f t="shared" si="9"/>
         <v>Plover - V - 0006</v>
       </c>
       <c r="K96" t="str">
-        <f>$E96</f>
-        <v>57880229-89481</v>
+        <f t="shared" si="10"/>
+        <v>57880228-71915</v>
       </c>
       <c r="L96" t="str">
-        <f>$F96</f>
-        <v>Turf 04</v>
+        <f t="shared" si="11"/>
+        <v>Turf 03</v>
       </c>
       <c r="M96">
-        <f t="shared" si="1"/>
-        <v>48</v>
+        <f t="shared" si="13"/>
+        <v>50</v>
       </c>
       <c r="N96" t="str">
-        <f>$J96&amp;" - "&amp;$L96</f>
-        <v>Plover - V - 0006 - Turf 04</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0006 - Turf 03</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B97" t="s">
         <v>22</v>
@@ -6639,16 +6614,16 @@
         <v>16</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="E97" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F97" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G97">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H97" t="str">
         <f>_xlfn.XLOOKUP($B97,Table24[Misname],Table24[Canonical],$B97)</f>
@@ -6656,27 +6631,27 @@
       </c>
       <c r="I97">
         <f>_xlfn.XLOOKUP($J97,Table4[ward_name],Table4[priority])</f>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J97" t="str">
-        <f>$H97&amp;" - "&amp;$C97&amp;" - "&amp;$D97</f>
-        <v>Plover - V - 0009</v>
+        <f t="shared" si="9"/>
+        <v>Plover - V - 0006</v>
       </c>
       <c r="K97" t="str">
-        <f>$E97</f>
-        <v>57880262-79574</v>
+        <f t="shared" si="10"/>
+        <v>57880229-89481</v>
       </c>
       <c r="L97" t="str">
-        <f>$F97</f>
-        <v>Turf 01</v>
+        <f t="shared" si="11"/>
+        <v>Turf 04</v>
       </c>
       <c r="M97">
-        <f t="shared" si="1"/>
-        <v>34</v>
+        <f t="shared" si="13"/>
+        <v>48</v>
       </c>
       <c r="N97" t="str">
-        <f>$J97&amp;" - "&amp;$L97</f>
-        <v>Plover - V - 0009 - Turf 01</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0006 - Turf 04</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
@@ -6693,13 +6668,13 @@
         <v>140</v>
       </c>
       <c r="E98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F98" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G98">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H98" t="str">
         <f>_xlfn.XLOOKUP($B98,Table24[Misname],Table24[Canonical],$B98)</f>
@@ -6710,24 +6685,24 @@
         <v>29</v>
       </c>
       <c r="J98" t="str">
-        <f>$H98&amp;" - "&amp;$C98&amp;" - "&amp;$D98</f>
+        <f t="shared" si="9"/>
         <v>Plover - V - 0009</v>
       </c>
       <c r="K98" t="str">
-        <f>$E98</f>
-        <v>57880263-54159</v>
+        <f t="shared" si="10"/>
+        <v>57880262-79574</v>
       </c>
       <c r="L98" t="str">
-        <f>$F98</f>
-        <v>Turf 02</v>
+        <f t="shared" si="11"/>
+        <v>Turf 01</v>
       </c>
       <c r="M98">
-        <f t="shared" si="1"/>
-        <v>32</v>
+        <f t="shared" si="13"/>
+        <v>34</v>
       </c>
       <c r="N98" t="str">
-        <f>$J98&amp;" - "&amp;$L98</f>
-        <v>Plover - V - 0009 - Turf 02</v>
+        <f t="shared" si="12"/>
+        <v>Plover - V - 0009 - Turf 01</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
@@ -6744,13 +6719,13 @@
         <v>140</v>
       </c>
       <c r="E99" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F99" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G99">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H99" t="str">
         <f>_xlfn.XLOOKUP($B99,Table24[Misname],Table24[Canonical],$B99)</f>
@@ -6761,80 +6736,80 @@
         <v>29</v>
       </c>
       <c r="J99" t="str">
-        <f>$H99&amp;" - "&amp;$C99&amp;" - "&amp;$D99</f>
+        <f t="shared" ref="J99:J130" si="14">$H99&amp;" - "&amp;$C99&amp;" - "&amp;$D99</f>
         <v>Plover - V - 0009</v>
       </c>
       <c r="K99" t="str">
-        <f>$E99</f>
-        <v>57880264-71725</v>
+        <f t="shared" ref="K99:K130" si="15">$E99</f>
+        <v>57880263-54159</v>
       </c>
       <c r="L99" t="str">
-        <f>$F99</f>
-        <v>Turf 03</v>
+        <f t="shared" ref="L99:L130" si="16">$F99</f>
+        <v>Turf 02</v>
       </c>
       <c r="M99">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f t="shared" si="13"/>
+        <v>32</v>
       </c>
       <c r="N99" t="str">
-        <f>$J99&amp;" - "&amp;$L99</f>
-        <v>Plover - V - 0009 - Turf 03</v>
+        <f t="shared" ref="N99:N130" si="17">$J99&amp;" - "&amp;$L99</f>
+        <v>Plover - V - 0009 - Turf 02</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B100" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E100" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F100" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G100">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H100" t="str">
         <f>_xlfn.XLOOKUP($B100,Table24[Misname],Table24[Canonical],$B100)</f>
-        <v>Stevens Point</v>
+        <v>Plover</v>
       </c>
       <c r="I100">
         <f>_xlfn.XLOOKUP($J100,Table4[ward_name],Table4[priority])</f>
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J100" t="str">
-        <f>$H100&amp;" - "&amp;$C100&amp;" - "&amp;$D100</f>
-        <v>Stevens Point - C - 0031</v>
+        <f t="shared" si="14"/>
+        <v>Plover - V - 0009</v>
       </c>
       <c r="K100" t="str">
-        <f>$E100</f>
-        <v>57880330-64792</v>
+        <f t="shared" si="15"/>
+        <v>57880264-71725</v>
       </c>
       <c r="L100" t="str">
-        <f>$F100</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 03</v>
       </c>
       <c r="M100">
-        <f t="shared" si="1"/>
-        <v>33</v>
+        <f t="shared" si="13"/>
+        <v>30</v>
       </c>
       <c r="N100" t="str">
-        <f>$J100&amp;" - "&amp;$L100</f>
-        <v>Stevens Point - C - 0031 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Plover - V - 0009 - Turf 03</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B101" t="s">
         <v>6</v>
@@ -6843,16 +6818,16 @@
         <v>7</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E101" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F101" t="s">
         <v>10</v>
       </c>
       <c r="G101">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H101" t="str">
         <f>_xlfn.XLOOKUP($B101,Table24[Misname],Table24[Canonical],$B101)</f>
@@ -6860,27 +6835,27 @@
       </c>
       <c r="I101">
         <f>_xlfn.XLOOKUP($J101,Table4[ward_name],Table4[priority])</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J101" t="str">
-        <f>$H101&amp;" - "&amp;$C101&amp;" - "&amp;$D101</f>
-        <v>Stevens Point - C - 0015</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0031</v>
       </c>
       <c r="K101" t="str">
-        <f>$E101</f>
-        <v>57880313-52713</v>
+        <f t="shared" si="15"/>
+        <v>57880330-64792</v>
       </c>
       <c r="L101" t="str">
-        <f>$F101</f>
+        <f t="shared" si="16"/>
         <v>Turf 01</v>
       </c>
       <c r="M101">
-        <f t="shared" si="1"/>
-        <v>36</v>
+        <f t="shared" si="13"/>
+        <v>33</v>
       </c>
       <c r="N101" t="str">
-        <f>$J101&amp;" - "&amp;$L101</f>
-        <v>Stevens Point - C - 0015 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0031 - Turf 01</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
@@ -6897,13 +6872,13 @@
         <v>146</v>
       </c>
       <c r="E102" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F102" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G102">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H102" t="str">
         <f>_xlfn.XLOOKUP($B102,Table24[Misname],Table24[Canonical],$B102)</f>
@@ -6914,24 +6889,24 @@
         <v>14</v>
       </c>
       <c r="J102" t="str">
-        <f>$H102&amp;" - "&amp;$C102&amp;" - "&amp;$D102</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0015</v>
       </c>
       <c r="K102" t="str">
-        <f>$E102</f>
-        <v>57880314-70280</v>
+        <f t="shared" si="15"/>
+        <v>57880313-52713</v>
       </c>
       <c r="L102" t="str">
-        <f>$F102</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M102">
-        <f t="shared" si="1"/>
-        <v>43</v>
+        <f t="shared" si="13"/>
+        <v>36</v>
       </c>
       <c r="N102" t="str">
-        <f>$J102&amp;" - "&amp;$L102</f>
-        <v>Stevens Point - C - 0015 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0015 - Turf 01</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
@@ -6948,13 +6923,13 @@
         <v>146</v>
       </c>
       <c r="E103" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F103" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G103">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H103" t="str">
         <f>_xlfn.XLOOKUP($B103,Table24[Misname],Table24[Canonical],$B103)</f>
@@ -6965,29 +6940,29 @@
         <v>14</v>
       </c>
       <c r="J103" t="str">
-        <f>$H103&amp;" - "&amp;$C103&amp;" - "&amp;$D103</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0015</v>
       </c>
       <c r="K103" t="str">
-        <f>$E103</f>
-        <v>57880315-30139</v>
+        <f t="shared" si="15"/>
+        <v>57880314-70280</v>
       </c>
       <c r="L103" t="str">
-        <f>$F103</f>
-        <v>Turf 03</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M103">
-        <f t="shared" si="1"/>
-        <v>52</v>
+        <f t="shared" si="13"/>
+        <v>43</v>
       </c>
       <c r="N103" t="str">
-        <f>$J103&amp;" - "&amp;$L103</f>
-        <v>Stevens Point - C - 0015 - Turf 03</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0015 - Turf 02</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B104" t="s">
         <v>6</v>
@@ -6996,16 +6971,16 @@
         <v>7</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E104" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F104" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G104">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H104" t="str">
         <f>_xlfn.XLOOKUP($B104,Table24[Misname],Table24[Canonical],$B104)</f>
@@ -7013,27 +6988,27 @@
       </c>
       <c r="I104">
         <f>_xlfn.XLOOKUP($J104,Table4[ward_name],Table4[priority])</f>
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="J104" t="str">
-        <f>$H104&amp;" - "&amp;$C104&amp;" - "&amp;$D104</f>
-        <v>Stevens Point - C - 0016</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0015</v>
       </c>
       <c r="K104" t="str">
-        <f>$E104</f>
-        <v>57880152-89254</v>
+        <f t="shared" si="15"/>
+        <v>57880315-30139</v>
       </c>
       <c r="L104" t="str">
-        <f>$F104</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 03</v>
       </c>
       <c r="M104">
-        <f t="shared" si="1"/>
-        <v>51</v>
+        <f t="shared" si="13"/>
+        <v>52</v>
       </c>
       <c r="N104" t="str">
-        <f>$J104&amp;" - "&amp;$L104</f>
-        <v>Stevens Point - C - 0016 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0015 - Turf 03</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
@@ -7050,13 +7025,13 @@
         <v>150</v>
       </c>
       <c r="E105" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F105" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G105">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H105" t="str">
         <f>_xlfn.XLOOKUP($B105,Table24[Misname],Table24[Canonical],$B105)</f>
@@ -7067,29 +7042,29 @@
         <v>42</v>
       </c>
       <c r="J105" t="str">
-        <f>$H105&amp;" - "&amp;$C105&amp;" - "&amp;$D105</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0016</v>
       </c>
       <c r="K105" t="str">
-        <f>$E105</f>
-        <v>57880153-34387</v>
+        <f t="shared" si="15"/>
+        <v>57880152-89254</v>
       </c>
       <c r="L105" t="str">
-        <f>$F105</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M105">
-        <f t="shared" si="1"/>
-        <v>49</v>
+        <f t="shared" si="13"/>
+        <v>51</v>
       </c>
       <c r="N105" t="str">
-        <f>$J105&amp;" - "&amp;$L105</f>
-        <v>Stevens Point - C - 0016 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0016 - Turf 01</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B106" t="s">
         <v>6</v>
@@ -7098,16 +7073,16 @@
         <v>7</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E106" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F106" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G106">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H106" t="str">
         <f>_xlfn.XLOOKUP($B106,Table24[Misname],Table24[Canonical],$B106)</f>
@@ -7115,27 +7090,27 @@
       </c>
       <c r="I106">
         <f>_xlfn.XLOOKUP($J106,Table4[ward_name],Table4[priority])</f>
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="J106" t="str">
-        <f>$H106&amp;" - "&amp;$C106&amp;" - "&amp;$D106</f>
-        <v>Stevens Point - C - 0011</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0016</v>
       </c>
       <c r="K106" t="str">
-        <f>$E106</f>
-        <v>57880075-60169</v>
+        <f t="shared" si="15"/>
+        <v>57880153-34387</v>
       </c>
       <c r="L106" t="str">
-        <f>$F106</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M106">
-        <f t="shared" si="1"/>
-        <v>32</v>
+        <f t="shared" si="13"/>
+        <v>49</v>
       </c>
       <c r="N106" t="str">
-        <f>$J106&amp;" - "&amp;$L106</f>
-        <v>Stevens Point - C - 0011 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0016 - Turf 02</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
@@ -7152,13 +7127,13 @@
         <v>153</v>
       </c>
       <c r="E107" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F107" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G107">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H107" t="str">
         <f>_xlfn.XLOOKUP($B107,Table24[Misname],Table24[Canonical],$B107)</f>
@@ -7169,24 +7144,24 @@
         <v>21</v>
       </c>
       <c r="J107" t="str">
-        <f>$H107&amp;" - "&amp;$C107&amp;" - "&amp;$D107</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0011</v>
       </c>
       <c r="K107" t="str">
-        <f>$E107</f>
-        <v>57880076-63010</v>
+        <f t="shared" si="15"/>
+        <v>57880075-60169</v>
       </c>
       <c r="L107" t="str">
-        <f>$F107</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M107">
-        <f t="shared" si="1"/>
-        <v>43</v>
+        <f t="shared" si="13"/>
+        <v>32</v>
       </c>
       <c r="N107" t="str">
-        <f>$J107&amp;" - "&amp;$L107</f>
-        <v>Stevens Point - C - 0011 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0011 - Turf 01</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
@@ -7203,13 +7178,13 @@
         <v>153</v>
       </c>
       <c r="E108" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F108" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G108">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H108" t="str">
         <f>_xlfn.XLOOKUP($B108,Table24[Misname],Table24[Canonical],$B108)</f>
@@ -7220,29 +7195,29 @@
         <v>21</v>
       </c>
       <c r="J108" t="str">
-        <f>$H108&amp;" - "&amp;$C108&amp;" - "&amp;$D108</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0011</v>
       </c>
       <c r="K108" t="str">
-        <f>$E108</f>
-        <v>57880077-55161</v>
+        <f t="shared" si="15"/>
+        <v>57880076-63010</v>
       </c>
       <c r="L108" t="str">
-        <f>$F108</f>
-        <v>Turf 03</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M108">
-        <f t="shared" si="1"/>
-        <v>45</v>
+        <f t="shared" si="13"/>
+        <v>43</v>
       </c>
       <c r="N108" t="str">
-        <f>$J108&amp;" - "&amp;$L108</f>
-        <v>Stevens Point - C - 0011 - Turf 03</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0011 - Turf 02</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B109" t="s">
         <v>6</v>
@@ -7251,16 +7226,16 @@
         <v>7</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E109" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F109" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G109">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H109" t="str">
         <f>_xlfn.XLOOKUP($B109,Table24[Misname],Table24[Canonical],$B109)</f>
@@ -7268,27 +7243,27 @@
       </c>
       <c r="I109">
         <f>_xlfn.XLOOKUP($J109,Table4[ward_name],Table4[priority])</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J109" t="str">
-        <f>$H109&amp;" - "&amp;$C109&amp;" - "&amp;$D109</f>
-        <v>Stevens Point - C - 0005</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0011</v>
       </c>
       <c r="K109" t="str">
-        <f>$E109</f>
-        <v>57880335-22607</v>
+        <f t="shared" si="15"/>
+        <v>57880077-55161</v>
       </c>
       <c r="L109" t="str">
-        <f>$F109</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 03</v>
       </c>
       <c r="M109">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="13"/>
+        <v>45</v>
       </c>
       <c r="N109" t="str">
-        <f>$J109&amp;" - "&amp;$L109</f>
-        <v>Stevens Point - C - 0005 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0011 - Turf 03</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
@@ -7305,10 +7280,10 @@
         <v>157</v>
       </c>
       <c r="E110" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F110" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G110">
         <v>53</v>
@@ -7322,75 +7297,75 @@
         <v>15</v>
       </c>
       <c r="J110" t="str">
-        <f>$H110&amp;" - "&amp;$C110&amp;" - "&amp;$D110</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0005</v>
       </c>
       <c r="K110" t="str">
-        <f>$E110</f>
-        <v>57880336-72467</v>
+        <f t="shared" si="15"/>
+        <v>57880335-22607</v>
       </c>
       <c r="L110" t="str">
-        <f>$F110</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>53</v>
       </c>
       <c r="N110" t="str">
-        <f>$J110&amp;" - "&amp;$L110</f>
-        <v>Stevens Point - C - 0005 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0005 - Turf 01</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B111" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="C111" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="E111" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F111" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G111">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="H111" t="str">
         <f>_xlfn.XLOOKUP($B111,Table24[Misname],Table24[Canonical],$B111)</f>
-        <v>Amherst</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I111">
         <f>_xlfn.XLOOKUP($J111,Table4[ward_name],Table4[priority])</f>
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="J111" t="str">
-        <f>$H111&amp;" - "&amp;$C111&amp;" - "&amp;$D111</f>
-        <v>Amherst - V - 0001</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0005</v>
       </c>
       <c r="K111" t="str">
-        <f>$E111</f>
-        <v>57880207-93883</v>
+        <f t="shared" si="15"/>
+        <v>57880336-72467</v>
       </c>
       <c r="L111" t="str">
-        <f>$F111</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M111">
-        <f t="shared" si="1"/>
-        <v>29</v>
+        <f t="shared" si="13"/>
+        <v>53</v>
       </c>
       <c r="N111" t="str">
-        <f>$J111&amp;" - "&amp;$L111</f>
-        <v>Amherst - V - 0001 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0005 - Turf 02</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
@@ -7407,13 +7382,13 @@
         <v>17</v>
       </c>
       <c r="E112" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F112" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G112">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H112" t="str">
         <f>_xlfn.XLOOKUP($B112,Table24[Misname],Table24[Canonical],$B112)</f>
@@ -7424,75 +7399,75 @@
         <v>45</v>
       </c>
       <c r="J112" t="str">
-        <f>$H112&amp;" - "&amp;$C112&amp;" - "&amp;$D112</f>
+        <f t="shared" si="14"/>
         <v>Amherst - V - 0001</v>
       </c>
       <c r="K112" t="str">
-        <f>$E112</f>
-        <v>57880208-21449</v>
+        <f t="shared" si="15"/>
+        <v>57880207-93883</v>
       </c>
       <c r="L112" t="str">
-        <f>$F112</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M112">
-        <f t="shared" si="1"/>
-        <v>34</v>
+        <f t="shared" si="13"/>
+        <v>29</v>
       </c>
       <c r="N112" t="str">
-        <f>$J112&amp;" - "&amp;$L112</f>
-        <v>Amherst - V - 0001 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Amherst - V - 0001 - Turf 01</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B113" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="C113" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="E113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F113" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G113">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H113" t="str">
         <f>_xlfn.XLOOKUP($B113,Table24[Misname],Table24[Canonical],$B113)</f>
-        <v>Stevens Point</v>
+        <v>Amherst</v>
       </c>
       <c r="I113">
         <f>_xlfn.XLOOKUP($J113,Table4[ward_name],Table4[priority])</f>
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="J113" t="str">
-        <f>$H113&amp;" - "&amp;$C113&amp;" - "&amp;$D113</f>
-        <v>Stevens Point - C - 0009</v>
+        <f t="shared" si="14"/>
+        <v>Amherst - V - 0001</v>
       </c>
       <c r="K113" t="str">
-        <f>$E113</f>
-        <v>57880090-99062</v>
+        <f t="shared" si="15"/>
+        <v>57880208-21449</v>
       </c>
       <c r="L113" t="str">
-        <f>$F113</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M113">
-        <f t="shared" si="1"/>
-        <v>45</v>
+        <f t="shared" si="13"/>
+        <v>34</v>
       </c>
       <c r="N113" t="str">
-        <f>$J113&amp;" - "&amp;$L113</f>
-        <v>Stevens Point - C - 0009 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Amherst - V - 0001 - Turf 02</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
@@ -7509,13 +7484,13 @@
         <v>140</v>
       </c>
       <c r="E114" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F114" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G114">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H114" t="str">
         <f>_xlfn.XLOOKUP($B114,Table24[Misname],Table24[Canonical],$B114)</f>
@@ -7526,24 +7501,24 @@
         <v>4</v>
       </c>
       <c r="J114" t="str">
-        <f>$H114&amp;" - "&amp;$C114&amp;" - "&amp;$D114</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0009</v>
       </c>
       <c r="K114" t="str">
-        <f>$E114</f>
-        <v>57880091-26628</v>
+        <f t="shared" si="15"/>
+        <v>57880090-99062</v>
       </c>
       <c r="L114" t="str">
-        <f>$F114</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M114">
-        <f t="shared" si="1"/>
-        <v>39</v>
+        <f t="shared" si="13"/>
+        <v>45</v>
       </c>
       <c r="N114" t="str">
-        <f>$J114&amp;" - "&amp;$L114</f>
-        <v>Stevens Point - C - 0009 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0009 - Turf 01</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
@@ -7560,13 +7535,13 @@
         <v>140</v>
       </c>
       <c r="E115" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F115" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G115">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H115" t="str">
         <f>_xlfn.XLOOKUP($B115,Table24[Misname],Table24[Canonical],$B115)</f>
@@ -7577,47 +7552,47 @@
         <v>4</v>
       </c>
       <c r="J115" t="str">
-        <f>$H115&amp;" - "&amp;$C115&amp;" - "&amp;$D115</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0009</v>
       </c>
       <c r="K115" t="str">
-        <f>$E115</f>
-        <v>57880092-44195</v>
+        <f t="shared" si="15"/>
+        <v>57880091-26628</v>
       </c>
       <c r="L115" t="str">
-        <f>$F115</f>
-        <v>Turf 03</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M115">
-        <f t="shared" si="1"/>
-        <v>33</v>
+        <f t="shared" si="13"/>
+        <v>39</v>
       </c>
       <c r="N115" t="str">
-        <f>$J115&amp;" - "&amp;$L115</f>
-        <v>Stevens Point - C - 0009 - Turf 03</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0009 - Turf 02</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C116" t="s">
         <v>7</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="E116" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F116" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G116">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H116" t="str">
         <f>_xlfn.XLOOKUP($B116,Table24[Misname],Table24[Canonical],$B116)</f>
@@ -7625,27 +7600,27 @@
       </c>
       <c r="I116">
         <f>_xlfn.XLOOKUP($J116,Table4[ward_name],Table4[priority])</f>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J116" t="str">
-        <f>$H116&amp;" - "&amp;$C116&amp;" - "&amp;$D116</f>
-        <v>Stevens Point - C - 0003</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0009</v>
       </c>
       <c r="K116" t="str">
-        <f>$E116</f>
-        <v>57880182-74164</v>
+        <f t="shared" si="15"/>
+        <v>57880092-44195</v>
       </c>
       <c r="L116" t="str">
-        <f>$F116</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 03</v>
       </c>
       <c r="M116">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f t="shared" si="13"/>
+        <v>33</v>
       </c>
       <c r="N116" t="str">
-        <f>$J116&amp;" - "&amp;$L116</f>
-        <v>Stevens Point - C - 0003 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0009 - Turf 03</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
@@ -7662,13 +7637,13 @@
         <v>106</v>
       </c>
       <c r="E117" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F117" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G117">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H117" t="str">
         <f>_xlfn.XLOOKUP($B117,Table24[Misname],Table24[Canonical],$B117)</f>
@@ -7679,29 +7654,29 @@
         <v>11</v>
       </c>
       <c r="J117" t="str">
-        <f>$H117&amp;" - "&amp;$C117&amp;" - "&amp;$D117</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0003</v>
       </c>
       <c r="K117" t="str">
-        <f>$E117</f>
-        <v>57880183-91731</v>
+        <f t="shared" si="15"/>
+        <v>57880182-74164</v>
       </c>
       <c r="L117" t="str">
-        <f>$F117</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M117">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f t="shared" si="13"/>
+        <v>35</v>
       </c>
       <c r="N117" t="str">
-        <f>$J117&amp;" - "&amp;$L117</f>
-        <v>Stevens Point - C - 0003 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0003 - Turf 01</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B118" t="s">
         <v>6</v>
@@ -7710,16 +7685,16 @@
         <v>7</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="E118" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F118" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G118">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="H118" t="str">
         <f>_xlfn.XLOOKUP($B118,Table24[Misname],Table24[Canonical],$B118)</f>
@@ -7727,27 +7702,27 @@
       </c>
       <c r="I118">
         <f>_xlfn.XLOOKUP($J118,Table4[ward_name],Table4[priority])</f>
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J118" t="str">
-        <f>$H118&amp;" - "&amp;$C118&amp;" - "&amp;$D118</f>
-        <v>Stevens Point - C - 0030</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0003</v>
       </c>
       <c r="K118" t="str">
-        <f>$E118</f>
-        <v>57880177-76804</v>
+        <f t="shared" si="15"/>
+        <v>57880183-91731</v>
       </c>
       <c r="L118" t="str">
-        <f>$F118</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M118">
-        <f t="shared" si="1"/>
-        <v>52</v>
+        <f t="shared" si="13"/>
+        <v>40</v>
       </c>
       <c r="N118" t="str">
-        <f>$J118&amp;" - "&amp;$L118</f>
-        <v>Stevens Point - C - 0030 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0003 - Turf 02</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
@@ -7764,13 +7739,13 @@
         <v>167</v>
       </c>
       <c r="E119" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F119" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G119">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H119" t="str">
         <f>_xlfn.XLOOKUP($B119,Table24[Misname],Table24[Canonical],$B119)</f>
@@ -7781,29 +7756,29 @@
         <v>32</v>
       </c>
       <c r="J119" t="str">
-        <f>$H119&amp;" - "&amp;$C119&amp;" - "&amp;$D119</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0030</v>
       </c>
       <c r="K119" t="str">
-        <f>$E119</f>
-        <v>57880178-79644</v>
+        <f t="shared" si="15"/>
+        <v>57880177-76804</v>
       </c>
       <c r="L119" t="str">
-        <f>$F119</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M119">
-        <f t="shared" si="1"/>
-        <v>47</v>
+        <f t="shared" si="13"/>
+        <v>52</v>
       </c>
       <c r="N119" t="str">
-        <f>$J119&amp;" - "&amp;$L119</f>
-        <v>Stevens Point - C - 0030 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0030 - Turf 01</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B120" t="s">
         <v>6</v>
@@ -7812,13 +7787,13 @@
         <v>7</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E120" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F120" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G120">
         <v>47</v>
@@ -7829,27 +7804,27 @@
       </c>
       <c r="I120">
         <f>_xlfn.XLOOKUP($J120,Table4[ward_name],Table4[priority])</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J120" t="str">
-        <f>$H120&amp;" - "&amp;$C120&amp;" - "&amp;$D120</f>
-        <v>Stevens Point - C - 0012</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0030</v>
       </c>
       <c r="K120" t="str">
-        <f>$E120</f>
-        <v>57880253-84880</v>
+        <f t="shared" si="15"/>
+        <v>57880178-79644</v>
       </c>
       <c r="L120" t="str">
-        <f>$F120</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M120">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>47</v>
       </c>
       <c r="N120" t="str">
-        <f>$J120&amp;" - "&amp;$L120</f>
-        <v>Stevens Point - C - 0012 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0030 - Turf 02</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
@@ -7866,13 +7841,13 @@
         <v>170</v>
       </c>
       <c r="E121" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F121" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G121">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H121" t="str">
         <f>_xlfn.XLOOKUP($B121,Table24[Misname],Table24[Canonical],$B121)</f>
@@ -7883,24 +7858,24 @@
         <v>28</v>
       </c>
       <c r="J121" t="str">
-        <f>$H121&amp;" - "&amp;$C121&amp;" - "&amp;$D121</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0012</v>
       </c>
       <c r="K121" t="str">
-        <f>$E121</f>
-        <v>57880254-59464</v>
+        <f t="shared" si="15"/>
+        <v>57880253-84880</v>
       </c>
       <c r="L121" t="str">
-        <f>$F121</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M121">
-        <f t="shared" si="1"/>
-        <v>44</v>
+        <f t="shared" si="13"/>
+        <v>47</v>
       </c>
       <c r="N121" t="str">
-        <f>$J121&amp;" - "&amp;$L121</f>
-        <v>Stevens Point - C - 0012 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0012 - Turf 01</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
@@ -7917,13 +7892,13 @@
         <v>170</v>
       </c>
       <c r="E122" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F122" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G122">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H122" t="str">
         <f>_xlfn.XLOOKUP($B122,Table24[Misname],Table24[Canonical],$B122)</f>
@@ -7934,75 +7909,75 @@
         <v>28</v>
       </c>
       <c r="J122" t="str">
-        <f>$H122&amp;" - "&amp;$C122&amp;" - "&amp;$D122</f>
+        <f t="shared" si="14"/>
         <v>Stevens Point - C - 0012</v>
       </c>
       <c r="K122" t="str">
-        <f>$E122</f>
-        <v>57880255-77031</v>
+        <f t="shared" si="15"/>
+        <v>57880254-59464</v>
       </c>
       <c r="L122" t="str">
-        <f>$F122</f>
-        <v>Turf 03</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M122">
-        <f t="shared" si="1"/>
-        <v>31</v>
+        <f t="shared" si="13"/>
+        <v>44</v>
       </c>
       <c r="N122" t="str">
-        <f>$J122&amp;" - "&amp;$L122</f>
-        <v>Stevens Point - C - 0012 - Turf 03</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0012 - Turf 02</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B123" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C123" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="E123" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F123" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G123">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H123" t="str">
         <f>_xlfn.XLOOKUP($B123,Table24[Misname],Table24[Canonical],$B123)</f>
-        <v>Plover</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I123">
         <f>_xlfn.XLOOKUP($J123,Table4[ward_name],Table4[priority])</f>
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="J123" t="str">
-        <f>$H123&amp;" - "&amp;$C123&amp;" - "&amp;$D123</f>
-        <v>Plover - V - 0008</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0012</v>
       </c>
       <c r="K123" t="str">
-        <f>$E123</f>
-        <v>57880256-73994</v>
+        <f t="shared" si="15"/>
+        <v>57880255-77031</v>
       </c>
       <c r="L123" t="str">
-        <f>$F123</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 03</v>
       </c>
       <c r="M123">
-        <f t="shared" si="1"/>
-        <v>29</v>
+        <f t="shared" si="13"/>
+        <v>31</v>
       </c>
       <c r="N123" t="str">
-        <f>$J123&amp;" - "&amp;$L123</f>
-        <v>Plover - V - 0008 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0012 - Turf 03</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
@@ -8019,13 +7994,13 @@
         <v>78</v>
       </c>
       <c r="E124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F124" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G124">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H124" t="str">
         <f>_xlfn.XLOOKUP($B124,Table24[Misname],Table24[Canonical],$B124)</f>
@@ -8036,24 +8011,24 @@
         <v>36</v>
       </c>
       <c r="J124" t="str">
-        <f>$H124&amp;" - "&amp;$C124&amp;" - "&amp;$D124</f>
+        <f t="shared" si="14"/>
         <v>Plover - V - 0008</v>
       </c>
       <c r="K124" t="str">
-        <f>$E124</f>
-        <v>57880257-91560</v>
+        <f t="shared" si="15"/>
+        <v>57880256-73994</v>
       </c>
       <c r="L124" t="str">
-        <f>$F124</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M124">
-        <f t="shared" si="1"/>
-        <v>34</v>
+        <f t="shared" si="13"/>
+        <v>29</v>
       </c>
       <c r="N124" t="str">
-        <f>$J124&amp;" - "&amp;$L124</f>
-        <v>Plover - V - 0008 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Plover - V - 0008 - Turf 01</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
@@ -8070,13 +8045,13 @@
         <v>78</v>
       </c>
       <c r="E125" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F125" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G125">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H125" t="str">
         <f>_xlfn.XLOOKUP($B125,Table24[Misname],Table24[Canonical],$B125)</f>
@@ -8087,126 +8062,126 @@
         <v>36</v>
       </c>
       <c r="J125" t="str">
-        <f>$H125&amp;" - "&amp;$C125&amp;" - "&amp;$D125</f>
+        <f t="shared" si="14"/>
         <v>Plover - V - 0008</v>
       </c>
       <c r="K125" t="str">
-        <f>$E125</f>
-        <v>57880258-66145</v>
+        <f t="shared" si="15"/>
+        <v>57880257-91560</v>
       </c>
       <c r="L125" t="str">
-        <f>$F125</f>
-        <v>Turf 03</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M125">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f t="shared" si="13"/>
+        <v>34</v>
       </c>
       <c r="N125" t="str">
-        <f>$J125&amp;" - "&amp;$L125</f>
-        <v>Plover - V - 0008 - Turf 03</v>
+        <f t="shared" si="17"/>
+        <v>Plover - V - 0008 - Turf 02</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B126" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C126" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E126" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F126" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G126">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="H126" t="str">
         <f>_xlfn.XLOOKUP($B126,Table24[Misname],Table24[Canonical],$B126)</f>
-        <v>Stevens Point</v>
+        <v>Plover</v>
       </c>
       <c r="I126">
         <f>_xlfn.XLOOKUP($J126,Table4[ward_name],Table4[priority])</f>
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J126" t="str">
-        <f>$H126&amp;" - "&amp;$C126&amp;" - "&amp;$D126</f>
-        <v>Stevens Point - C - 0006</v>
+        <f t="shared" si="14"/>
+        <v>Plover - V - 0008</v>
       </c>
       <c r="K126" t="str">
-        <f>$E126</f>
-        <v>57880312-90203</v>
+        <f t="shared" si="15"/>
+        <v>57880258-66145</v>
       </c>
       <c r="L126" t="str">
-        <f>$F126</f>
-        <v>Turf 01</v>
+        <f t="shared" si="16"/>
+        <v>Turf 03</v>
       </c>
       <c r="M126">
-        <f t="shared" si="1"/>
-        <v>57</v>
+        <f t="shared" si="13"/>
+        <v>30</v>
       </c>
       <c r="N126" t="str">
-        <f>$J126&amp;" - "&amp;$L126</f>
-        <v>Stevens Point - C - 0006 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Plover - V - 0008 - Turf 03</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B127" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="E127" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F127" t="s">
         <v>10</v>
       </c>
       <c r="G127">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H127" t="str">
         <f>_xlfn.XLOOKUP($B127,Table24[Misname],Table24[Canonical],$B127)</f>
-        <v>Plover</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I127">
         <f>_xlfn.XLOOKUP($J127,Table4[ward_name],Table4[priority])</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="J127" t="str">
-        <f>$H127&amp;" - "&amp;$C127&amp;" - "&amp;$D127</f>
-        <v>Plover - V - 0005</v>
+        <f t="shared" si="14"/>
+        <v>Stevens Point - C - 0006</v>
       </c>
       <c r="K127" t="str">
-        <f>$E127</f>
-        <v>57880201-74752</v>
+        <f t="shared" si="15"/>
+        <v>57880312-90203</v>
       </c>
       <c r="L127" t="str">
-        <f>$F127</f>
+        <f t="shared" si="16"/>
         <v>Turf 01</v>
       </c>
       <c r="M127">
-        <f t="shared" si="1"/>
-        <v>41</v>
+        <f t="shared" si="13"/>
+        <v>57</v>
       </c>
       <c r="N127" t="str">
-        <f>$J127&amp;" - "&amp;$L127</f>
-        <v>Plover - V - 0005 - Turf 01</v>
+        <f t="shared" si="17"/>
+        <v>Stevens Point - C - 0006 - Turf 01</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
@@ -8223,13 +8198,13 @@
         <v>157</v>
       </c>
       <c r="E128" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F128" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G128">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H128" t="str">
         <f>_xlfn.XLOOKUP($B128,Table24[Misname],Table24[Canonical],$B128)</f>
@@ -8240,24 +8215,24 @@
         <v>40</v>
       </c>
       <c r="J128" t="str">
-        <f>$H128&amp;" - "&amp;$C128&amp;" - "&amp;$D128</f>
+        <f t="shared" si="14"/>
         <v>Plover - V - 0005</v>
       </c>
       <c r="K128" t="str">
-        <f>$E128</f>
-        <v>57880202-92318</v>
+        <f t="shared" si="15"/>
+        <v>57880201-74752</v>
       </c>
       <c r="L128" t="str">
-        <f>$F128</f>
-        <v>Turf 02</v>
+        <f t="shared" si="16"/>
+        <v>Turf 01</v>
       </c>
       <c r="M128">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f t="shared" si="13"/>
+        <v>41</v>
       </c>
       <c r="N128" t="str">
-        <f>$J128&amp;" - "&amp;$L128</f>
-        <v>Plover - V - 0005 - Turf 02</v>
+        <f t="shared" si="17"/>
+        <v>Plover - V - 0005 - Turf 01</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
@@ -8274,13 +8249,13 @@
         <v>157</v>
       </c>
       <c r="E129" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F129" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G129">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="H129" t="str">
         <f>_xlfn.XLOOKUP($B129,Table24[Misname],Table24[Canonical],$B129)</f>
@@ -8291,24 +8266,24 @@
         <v>40</v>
       </c>
       <c r="J129" t="str">
-        <f>$H129&amp;" - "&amp;$C129&amp;" - "&amp;$D129</f>
+        <f t="shared" si="14"/>
         <v>Plover - V - 0005</v>
       </c>
       <c r="K129" t="str">
-        <f>$E129</f>
-        <v>57880203-52177</v>
+        <f t="shared" si="15"/>
+        <v>57880202-92318</v>
       </c>
       <c r="L129" t="str">
-        <f>$F129</f>
-        <v>Turf 03</v>
+        <f t="shared" si="16"/>
+        <v>Turf 02</v>
       </c>
       <c r="M129">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="13"/>
+        <v>35</v>
       </c>
       <c r="N129" t="str">
-        <f>$J129&amp;" - "&amp;$L129</f>
-        <v>Plover - V - 0005 - Turf 03</v>
+        <f t="shared" si="17"/>
+        <v>Plover - V - 0005 - Turf 02</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
@@ -8325,13 +8300,13 @@
         <v>157</v>
       </c>
       <c r="E130" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F130" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G130">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H130" t="str">
         <f>_xlfn.XLOOKUP($B130,Table24[Misname],Table24[Canonical],$B130)</f>
@@ -8342,75 +8317,75 @@
         <v>40</v>
       </c>
       <c r="J130" t="str">
-        <f>$H130&amp;" - "&amp;$C130&amp;" - "&amp;$D130</f>
+        <f t="shared" si="14"/>
         <v>Plover - V - 0005</v>
       </c>
       <c r="K130" t="str">
-        <f>$E130</f>
-        <v>57880204-12036</v>
+        <f t="shared" si="15"/>
+        <v>57880203-52177</v>
       </c>
       <c r="L130" t="str">
-        <f>$F130</f>
-        <v>Turf 04</v>
+        <f t="shared" si="16"/>
+        <v>Turf 03</v>
       </c>
       <c r="M130">
-        <f t="shared" si="1"/>
-        <v>54</v>
+        <f t="shared" si="13"/>
+        <v>53</v>
       </c>
       <c r="N130" t="str">
-        <f>$J130&amp;" - "&amp;$L130</f>
-        <v>Plover - V - 0005 - Turf 04</v>
+        <f t="shared" si="17"/>
+        <v>Plover - V - 0005 - Turf 03</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C131" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="E131" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F131" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G131">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H131" t="str">
         <f>_xlfn.XLOOKUP($B131,Table24[Misname],Table24[Canonical],$B131)</f>
-        <v>Stevens Point</v>
+        <v>Plover</v>
       </c>
       <c r="I131">
         <f>_xlfn.XLOOKUP($J131,Table4[ward_name],Table4[priority])</f>
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="J131" t="str">
-        <f>$H131&amp;" - "&amp;$C131&amp;" - "&amp;$D131</f>
-        <v>Stevens Point - C - 0013</v>
+        <f t="shared" ref="J131:J139" si="18">$H131&amp;" - "&amp;$C131&amp;" - "&amp;$D131</f>
+        <v>Plover - V - 0005</v>
       </c>
       <c r="K131" t="str">
-        <f>$E131</f>
-        <v>57880048-53199</v>
+        <f t="shared" ref="K131:K139" si="19">$E131</f>
+        <v>57880204-12036</v>
       </c>
       <c r="L131" t="str">
-        <f>$F131</f>
-        <v>Turf 01</v>
+        <f t="shared" ref="L131:L139" si="20">$F131</f>
+        <v>Turf 04</v>
       </c>
       <c r="M131">
-        <f t="shared" ref="M131:M135" si="2">$G131</f>
-        <v>44</v>
+        <f t="shared" si="13"/>
+        <v>54</v>
       </c>
       <c r="N131" t="str">
-        <f>$J131&amp;" - "&amp;$L131</f>
-        <v>Stevens Point - C - 0013 - Turf 01</v>
+        <f t="shared" ref="N131:N139" si="21">$J131&amp;" - "&amp;$L131</f>
+        <v>Plover - V - 0005 - Turf 04</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
@@ -8427,13 +8402,13 @@
         <v>182</v>
       </c>
       <c r="E132" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F132" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G132">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H132" t="str">
         <f>_xlfn.XLOOKUP($B132,Table24[Misname],Table24[Canonical],$B132)</f>
@@ -8444,75 +8419,75 @@
         <v>2</v>
       </c>
       <c r="J132" t="str">
-        <f>$H132&amp;" - "&amp;$C132&amp;" - "&amp;$D132</f>
+        <f t="shared" si="18"/>
         <v>Stevens Point - C - 0013</v>
       </c>
       <c r="K132" t="str">
-        <f>$E132</f>
-        <v>57880049-13058</v>
+        <f t="shared" si="19"/>
+        <v>57880048-53199</v>
       </c>
       <c r="L132" t="str">
-        <f>$F132</f>
-        <v>Turf 02</v>
+        <f t="shared" si="20"/>
+        <v>Turf 01</v>
       </c>
       <c r="M132">
-        <f t="shared" si="2"/>
-        <v>42</v>
+        <f t="shared" ref="M132:M136" si="22">$G132</f>
+        <v>44</v>
       </c>
       <c r="N132" t="str">
-        <f>$J132&amp;" - "&amp;$L132</f>
-        <v>Stevens Point - C - 0013 - Turf 02</v>
+        <f t="shared" si="21"/>
+        <v>Stevens Point - C - 0013 - Turf 01</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B133" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C133" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>43</v>
+        <v>182</v>
       </c>
       <c r="E133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F133" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G133">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H133" t="str">
         <f>_xlfn.XLOOKUP($B133,Table24[Misname],Table24[Canonical],$B133)</f>
-        <v>Plover</v>
+        <v>Stevens Point</v>
       </c>
       <c r="I133">
         <f>_xlfn.XLOOKUP($J133,Table4[ward_name],Table4[priority])</f>
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="J133" t="str">
-        <f>$H133&amp;" - "&amp;$C133&amp;" - "&amp;$D133</f>
-        <v>Plover - V - 0002</v>
+        <f t="shared" si="18"/>
+        <v>Stevens Point - C - 0013</v>
       </c>
       <c r="K133" t="str">
-        <f>$E133</f>
-        <v>57880080-15426</v>
+        <f t="shared" si="19"/>
+        <v>57880049-13058</v>
       </c>
       <c r="L133" t="str">
-        <f>$F133</f>
-        <v>Turf 01</v>
+        <f t="shared" si="20"/>
+        <v>Turf 02</v>
       </c>
       <c r="M133">
-        <f t="shared" si="2"/>
-        <v>11</v>
+        <f t="shared" si="22"/>
+        <v>42</v>
       </c>
       <c r="N133" t="str">
-        <f>$J133&amp;" - "&amp;$L133</f>
-        <v>Plover - V - 0002 - Turf 01</v>
+        <f t="shared" si="21"/>
+        <v>Stevens Point - C - 0013 - Turf 02</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
@@ -8529,13 +8504,13 @@
         <v>43</v>
       </c>
       <c r="E134" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F134" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G134">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H134" t="str">
         <f>_xlfn.XLOOKUP($B134,Table24[Misname],Table24[Canonical],$B134)</f>
@@ -8546,24 +8521,24 @@
         <v>47</v>
       </c>
       <c r="J134" t="str">
-        <f>$H134&amp;" - "&amp;$C134&amp;" - "&amp;$D134</f>
+        <f t="shared" si="18"/>
         <v>Plover - V - 0002</v>
       </c>
       <c r="K134" t="str">
-        <f>$E134</f>
-        <v>57880081-32993</v>
+        <f t="shared" si="19"/>
+        <v>57880080-15426</v>
       </c>
       <c r="L134" t="str">
-        <f>$F134</f>
-        <v>Turf 02</v>
+        <f t="shared" si="20"/>
+        <v>Turf 01</v>
       </c>
       <c r="M134">
-        <f t="shared" si="2"/>
-        <v>45</v>
+        <f t="shared" si="22"/>
+        <v>11</v>
       </c>
       <c r="N134" t="str">
-        <f>$J134&amp;" - "&amp;$L134</f>
-        <v>Plover - V - 0002 - Turf 02</v>
+        <f t="shared" si="21"/>
+        <v>Plover - V - 0002 - Turf 01</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
@@ -8580,13 +8555,13 @@
         <v>43</v>
       </c>
       <c r="E135" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F135" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G135">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H135" t="str">
         <f>_xlfn.XLOOKUP($B135,Table24[Misname],Table24[Canonical],$B135)</f>
@@ -8597,24 +8572,24 @@
         <v>47</v>
       </c>
       <c r="J135" t="str">
-        <f>$H135&amp;" - "&amp;$C135&amp;" - "&amp;$D135</f>
+        <f t="shared" si="18"/>
         <v>Plover - V - 0002</v>
       </c>
       <c r="K135" t="str">
-        <f>$E135</f>
-        <v>57880082-50560</v>
+        <f t="shared" si="19"/>
+        <v>57880081-32993</v>
       </c>
       <c r="L135" t="str">
-        <f>$F135</f>
-        <v>Turf 03</v>
+        <f t="shared" si="20"/>
+        <v>Turf 02</v>
       </c>
       <c r="M135">
-        <f t="shared" si="2"/>
-        <v>21</v>
+        <f t="shared" si="22"/>
+        <v>45</v>
       </c>
       <c r="N135" t="str">
-        <f>$J135&amp;" - "&amp;$L135</f>
-        <v>Plover - V - 0002 - Turf 03</v>
+        <f t="shared" si="21"/>
+        <v>Plover - V - 0002 - Turf 02</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
@@ -8631,13 +8606,13 @@
         <v>43</v>
       </c>
       <c r="E136" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F136" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G136">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H136" t="str">
         <f>_xlfn.XLOOKUP($B136,Table24[Misname],Table24[Canonical],$B136)</f>
@@ -8648,24 +8623,24 @@
         <v>47</v>
       </c>
       <c r="J136" t="str">
-        <f>$H136&amp;" - "&amp;$C136&amp;" - "&amp;$D136</f>
+        <f t="shared" si="18"/>
         <v>Plover - V - 0002</v>
       </c>
       <c r="K136" t="str">
-        <f>$E136</f>
-        <v>57880080-15426</v>
+        <f t="shared" si="19"/>
+        <v>57880082-50560</v>
       </c>
       <c r="L136" t="str">
-        <f>$F136</f>
-        <v>Turf 01</v>
+        <f t="shared" si="20"/>
+        <v>Turf 03</v>
       </c>
       <c r="M136">
-        <f t="shared" ref="M136:M138" si="3">$G136</f>
-        <v>11</v>
+        <f t="shared" si="22"/>
+        <v>21</v>
       </c>
       <c r="N136" t="str">
-        <f>$J136&amp;" - "&amp;$L136</f>
-        <v>Plover - V - 0002 - Turf 01</v>
+        <f t="shared" si="21"/>
+        <v>Plover - V - 0002 - Turf 03</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
@@ -8682,13 +8657,13 @@
         <v>43</v>
       </c>
       <c r="E137" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F137" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G137">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H137" t="str">
         <f>_xlfn.XLOOKUP($B137,Table24[Misname],Table24[Canonical],$B137)</f>
@@ -8699,24 +8674,24 @@
         <v>47</v>
       </c>
       <c r="J137" t="str">
-        <f>$H137&amp;" - "&amp;$C137&amp;" - "&amp;$D137</f>
+        <f t="shared" si="18"/>
         <v>Plover - V - 0002</v>
       </c>
       <c r="K137" t="str">
-        <f>$E137</f>
-        <v>57880081-32993</v>
+        <f t="shared" si="19"/>
+        <v>57880080-15426</v>
       </c>
       <c r="L137" t="str">
-        <f>$F137</f>
-        <v>Turf 02</v>
+        <f t="shared" si="20"/>
+        <v>Turf 01</v>
       </c>
       <c r="M137">
-        <f t="shared" si="3"/>
-        <v>45</v>
+        <f t="shared" ref="M137:M139" si="23">$G137</f>
+        <v>11</v>
       </c>
       <c r="N137" t="str">
-        <f>$J137&amp;" - "&amp;$L137</f>
-        <v>Plover - V - 0002 - Turf 02</v>
+        <f t="shared" si="21"/>
+        <v>Plover - V - 0002 - Turf 01</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
@@ -8733,13 +8708,13 @@
         <v>43</v>
       </c>
       <c r="E138" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F138" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G138">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H138" t="str">
         <f>_xlfn.XLOOKUP($B138,Table24[Misname],Table24[Canonical],$B138)</f>
@@ -8750,29 +8725,80 @@
         <v>47</v>
       </c>
       <c r="J138" t="str">
-        <f>$H138&amp;" - "&amp;$C138&amp;" - "&amp;$D138</f>
+        <f t="shared" si="18"/>
         <v>Plover - V - 0002</v>
       </c>
       <c r="K138" t="str">
-        <f>$E138</f>
+        <f t="shared" si="19"/>
+        <v>57880081-32993</v>
+      </c>
+      <c r="L138" t="str">
+        <f t="shared" si="20"/>
+        <v>Turf 02</v>
+      </c>
+      <c r="M138">
+        <f t="shared" si="23"/>
+        <v>45</v>
+      </c>
+      <c r="N138" t="str">
+        <f t="shared" si="21"/>
+        <v>Plover - V - 0002 - Turf 02</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>299</v>
+      </c>
+      <c r="B139" t="s">
+        <v>22</v>
+      </c>
+      <c r="C139" t="s">
+        <v>16</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E139" t="s">
+        <v>187</v>
+      </c>
+      <c r="F139" t="s">
+        <v>21</v>
+      </c>
+      <c r="G139">
+        <v>21</v>
+      </c>
+      <c r="H139" t="str">
+        <f>_xlfn.XLOOKUP($B139,Table24[Misname],Table24[Canonical],$B139)</f>
+        <v>Plover</v>
+      </c>
+      <c r="I139">
+        <f>_xlfn.XLOOKUP($J139,Table4[ward_name],Table4[priority])</f>
+        <v>47</v>
+      </c>
+      <c r="J139" t="str">
+        <f t="shared" si="18"/>
+        <v>Plover - V - 0002</v>
+      </c>
+      <c r="K139" t="str">
+        <f t="shared" si="19"/>
         <v>57880082-50560</v>
       </c>
-      <c r="L138" t="str">
-        <f>$F138</f>
+      <c r="L139" t="str">
+        <f t="shared" si="20"/>
         <v>Turf 03</v>
       </c>
-      <c r="M138">
-        <f t="shared" si="3"/>
+      <c r="M139">
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
-      <c r="N138" t="str">
-        <f>$J138&amp;" - "&amp;$L138</f>
+      <c r="N139" t="str">
+        <f t="shared" si="21"/>
         <v>Plover - V - 0002 - Turf 03</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N2:N138">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="N3:N139">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8812,8 +8838,8 @@
         <v>194</v>
       </c>
       <c r="C2">
-        <f>COUNTIF(Table7[priority],$B2)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -8824,8 +8850,8 @@
         <v>195</v>
       </c>
       <c r="C3">
-        <f>COUNTIF(Table7[priority],$B3)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -8836,8 +8862,8 @@
         <v>196</v>
       </c>
       <c r="C4">
-        <f>COUNTIF(Table7[priority],$B4)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B4)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -8848,8 +8874,8 @@
         <v>197</v>
       </c>
       <c r="C5">
-        <f>COUNTIF(Table7[priority],$B5)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B5)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -8860,8 +8886,8 @@
         <v>198</v>
       </c>
       <c r="C6">
-        <f>COUNTIF(Table7[priority],$B6)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B6)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -8872,8 +8898,8 @@
         <v>199</v>
       </c>
       <c r="C7">
-        <f>COUNTIF(Table7[priority],$B7)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B7)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -8884,8 +8910,8 @@
         <v>200</v>
       </c>
       <c r="C8">
-        <f>COUNTIF(Table7[priority],$B8)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B8)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -8896,8 +8922,8 @@
         <v>201</v>
       </c>
       <c r="C9">
-        <f>COUNTIF(Table7[priority],$B9)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B9)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -8908,8 +8934,8 @@
         <v>202</v>
       </c>
       <c r="C10">
-        <f>COUNTIF(Table7[priority],$B10)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B10)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -8920,8 +8946,8 @@
         <v>203</v>
       </c>
       <c r="C11">
-        <f>COUNTIF(Table7[priority],$B11)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B11)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -8932,8 +8958,8 @@
         <v>204</v>
       </c>
       <c r="C12">
-        <f>COUNTIF(Table7[priority],$B12)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B12)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -8944,8 +8970,8 @@
         <v>205</v>
       </c>
       <c r="C13">
-        <f>COUNTIF(Table7[priority],$B13)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B13)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -8956,8 +8982,8 @@
         <v>206</v>
       </c>
       <c r="C14">
-        <f>COUNTIF(Table7[priority],$B14)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B14)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -8968,8 +8994,8 @@
         <v>207</v>
       </c>
       <c r="C15">
-        <f>COUNTIF(Table7[priority],$B15)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B15)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -8980,8 +9006,8 @@
         <v>208</v>
       </c>
       <c r="C16">
-        <f>COUNTIF(Table7[priority],$B16)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B16)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -8992,8 +9018,8 @@
         <v>209</v>
       </c>
       <c r="C17">
-        <f>COUNTIF(Table7[priority],$B17)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B17)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -9004,8 +9030,8 @@
         <v>210</v>
       </c>
       <c r="C18">
-        <f>COUNTIF(Table7[priority],$B18)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B18)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -9016,8 +9042,8 @@
         <v>211</v>
       </c>
       <c r="C19">
-        <f>COUNTIF(Table7[priority],$B19)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B19)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -9028,8 +9054,8 @@
         <v>212</v>
       </c>
       <c r="C20">
-        <f>COUNTIF(Table7[priority],$B20)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B20)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -9040,8 +9066,8 @@
         <v>213</v>
       </c>
       <c r="C21">
-        <f>COUNTIF(Table7[priority],$B21)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B21)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -9052,8 +9078,8 @@
         <v>214</v>
       </c>
       <c r="C22">
-        <f>COUNTIF(Table7[priority],$B22)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B22)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -9064,8 +9090,8 @@
         <v>215</v>
       </c>
       <c r="C23">
-        <f>COUNTIF(Table7[priority],$B23)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B23)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -9076,8 +9102,8 @@
         <v>216</v>
       </c>
       <c r="C24">
-        <f>COUNTIF(Table7[priority],$B24)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B24)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -9088,8 +9114,8 @@
         <v>217</v>
       </c>
       <c r="C25">
-        <f>COUNTIF(Table7[priority],$B25)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B25)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -9100,8 +9126,8 @@
         <v>218</v>
       </c>
       <c r="C26">
-        <f>COUNTIF(Table7[priority],$B26)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B26)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -9112,8 +9138,8 @@
         <v>219</v>
       </c>
       <c r="C27">
-        <f>COUNTIF(Table7[priority],$B27)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B27)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -9124,8 +9150,8 @@
         <v>220</v>
       </c>
       <c r="C28">
-        <f>COUNTIF(Table7[priority],$B28)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B28)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -9136,8 +9162,8 @@
         <v>221</v>
       </c>
       <c r="C29">
-        <f>COUNTIF(Table7[priority],$B29)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B29)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -9148,8 +9174,8 @@
         <v>222</v>
       </c>
       <c r="C30">
-        <f>COUNTIF(Table7[priority],$B30)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B30)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -9160,8 +9186,8 @@
         <v>223</v>
       </c>
       <c r="C31">
-        <f>COUNTIF(Table7[priority],$B31)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B31)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -9172,8 +9198,8 @@
         <v>224</v>
       </c>
       <c r="C32">
-        <f>COUNTIF(Table7[priority],$B32)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B32)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -9184,8 +9210,8 @@
         <v>225</v>
       </c>
       <c r="C33">
-        <f>COUNTIF(Table7[priority],$B33)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B33)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -9196,8 +9222,8 @@
         <v>226</v>
       </c>
       <c r="C34">
-        <f>COUNTIF(Table7[priority],$B34)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B34)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -9208,8 +9234,8 @@
         <v>227</v>
       </c>
       <c r="C35">
-        <f>COUNTIF(Table7[priority],$B35)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B35)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -9220,8 +9246,8 @@
         <v>228</v>
       </c>
       <c r="C36">
-        <f>COUNTIF(Table7[priority],$B36)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B36)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -9232,8 +9258,8 @@
         <v>229</v>
       </c>
       <c r="C37">
-        <f>COUNTIF(Table7[priority],$B37)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B37)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -9244,7 +9270,7 @@
         <v>230</v>
       </c>
       <c r="C38">
-        <f>COUNTIF(Table7[priority],$B38)</f>
+        <f>COUNTIF(Table7[ward_from_turf],$B38)</f>
         <v>0</v>
       </c>
     </row>
@@ -9256,7 +9282,7 @@
         <v>231</v>
       </c>
       <c r="C39">
-        <f>COUNTIF(Table7[priority],$B39)</f>
+        <f>COUNTIF(Table7[ward_from_turf],$B39)</f>
         <v>0</v>
       </c>
     </row>
@@ -9268,7 +9294,7 @@
         <v>232</v>
       </c>
       <c r="C40">
-        <f>COUNTIF(Table7[priority],$B40)</f>
+        <f>COUNTIF(Table7[ward_from_turf],$B40)</f>
         <v>0</v>
       </c>
     </row>
@@ -9280,8 +9306,8 @@
         <v>233</v>
       </c>
       <c r="C41">
-        <f>COUNTIF(Table7[priority],$B41)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B41)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -9292,8 +9318,8 @@
         <v>234</v>
       </c>
       <c r="C42">
-        <f>COUNTIF(Table7[priority],$B42)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B42)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -9304,8 +9330,8 @@
         <v>235</v>
       </c>
       <c r="C43">
-        <f>COUNTIF(Table7[priority],$B43)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B43)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -9316,8 +9342,8 @@
         <v>236</v>
       </c>
       <c r="C44">
-        <f>COUNTIF(Table7[priority],$B44)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B44)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -9328,8 +9354,8 @@
         <v>237</v>
       </c>
       <c r="C45">
-        <f>COUNTIF(Table7[priority],$B45)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B45)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -9340,8 +9366,8 @@
         <v>238</v>
       </c>
       <c r="C46">
-        <f>COUNTIF(Table7[priority],$B46)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B46)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -9352,8 +9378,8 @@
         <v>239</v>
       </c>
       <c r="C47">
-        <f>COUNTIF(Table7[priority],$B47)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B47)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -9364,8 +9390,8 @@
         <v>240</v>
       </c>
       <c r="C48">
-        <f>COUNTIF(Table7[priority],$B48)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B48)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -9376,8 +9402,8 @@
         <v>241</v>
       </c>
       <c r="C49">
-        <f>COUNTIF(Table7[priority],$B49)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B49)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -9388,8 +9414,8 @@
         <v>242</v>
       </c>
       <c r="C50">
-        <f>COUNTIF(Table7[priority],$B50)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B50)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -9400,8 +9426,8 @@
         <v>243</v>
       </c>
       <c r="C51">
-        <f>COUNTIF(Table7[priority],$B51)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B51)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -9412,8 +9438,8 @@
         <v>244</v>
       </c>
       <c r="C52">
-        <f>COUNTIF(Table7[priority],$B52)</f>
-        <v>0</v>
+        <f>COUNTIF(Table7[ward_from_turf],$B52)</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
